--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F33E49F-1EE7-4DD9-85D3-937C3435FD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{718697AD-6804-4364-B464-3C5139092EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" firstSheet="7" activeTab="7" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" firstSheet="8" activeTab="17" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
   <sheets>
     <sheet name="Class_Enrollment" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="269">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -12322,7 +12322,7 @@
         <v>191</v>
       </c>
       <c r="B7" s="6">
-        <v>46170</v>
+        <v>46142</v>
       </c>
       <c r="C7" s="12" t="b">
         <v>0</v>
@@ -12334,15 +12334,21 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
+      <c r="B8" s="6">
+        <v>46170</v>
+      </c>
       <c r="C8" s="12" t="b">
         <v>0</v>
       </c>
       <c r="D8" s="12" t="b">
         <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -17724,7 +17730,7 @@
         <v>203</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -17816,20 +17822,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18016,11 +18022,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{718697AD-6804-4364-B464-3C5139092EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{939FDB2E-C4A6-4693-AE53-A8B67AE873C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" firstSheet="8" activeTab="17" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" firstSheet="17" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
   <sheets>
     <sheet name="Class_Enrollment" sheetId="1" r:id="rId1"/>
@@ -4445,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="b">
         <v>0</v>
@@ -17830,15 +17830,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -18021,14 +18012,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}"/>
 </file>
--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{939FDB2E-C4A6-4693-AE53-A8B67AE873C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A10EC84-889A-41AA-980E-2FD2A8934114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" firstSheet="17" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
@@ -3335,13 +3335,13 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="b">
         <v>1</v>
@@ -4451,13 +4451,13 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="b">
         <v>1</v>

--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -1,41 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A10EC84-889A-41AA-980E-2FD2A8934114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377D626C-D8CE-D34C-AF93-A393D658E996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" firstSheet="17" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17240" activeTab="2" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
   <sheets>
     <sheet name="Class_Enrollment" sheetId="1" r:id="rId1"/>
     <sheet name="Neo SIM" sheetId="16" r:id="rId2"/>
-    <sheet name="Airway SIM" sheetId="15" r:id="rId3"/>
-    <sheet name="Airway Decision SIM" sheetId="14" r:id="rId4"/>
-    <sheet name="TDAC" sheetId="25" r:id="rId5"/>
-    <sheet name="Micro SIM" sheetId="13" r:id="rId6"/>
-    <sheet name="CRM" sheetId="3" r:id="rId7"/>
-    <sheet name="PFCCS" sheetId="24" r:id="rId8"/>
-    <sheet name="FCCS" sheetId="9" r:id="rId9"/>
-    <sheet name="Wed SM Q1" sheetId="5" r:id="rId10"/>
-    <sheet name="Thurs SM Q1" sheetId="7" r:id="rId11"/>
-    <sheet name="Wed SM Q2" sheetId="18" r:id="rId12"/>
-    <sheet name="Thurs SM Q2" sheetId="21" r:id="rId13"/>
-    <sheet name="Wed SM Q3" sheetId="19" r:id="rId14"/>
-    <sheet name="Thurs SM Q3" sheetId="22" r:id="rId15"/>
-    <sheet name="Wed SM Q4" sheetId="20" r:id="rId16"/>
-    <sheet name="Thurs SM Q4" sheetId="23" r:id="rId17"/>
-    <sheet name="STABLE" sheetId="6" r:id="rId18"/>
-    <sheet name="OB Lite" sheetId="10" r:id="rId19"/>
-    <sheet name="OB SIM" sheetId="8" r:id="rId20"/>
-    <sheet name="ATLS" sheetId="17" r:id="rId21"/>
-    <sheet name="Course Dates Reference" sheetId="4" r:id="rId22"/>
-    <sheet name="CCEMT CRM Sched" sheetId="11" r:id="rId23"/>
+    <sheet name="FY26 Audiology Testing" sheetId="26" r:id="rId3"/>
+    <sheet name="Airway SIM" sheetId="15" r:id="rId4"/>
+    <sheet name="Airway Decision SIM" sheetId="14" r:id="rId5"/>
+    <sheet name="TDAC" sheetId="25" r:id="rId6"/>
+    <sheet name="Micro SIM" sheetId="13" r:id="rId7"/>
+    <sheet name="CRM" sheetId="3" r:id="rId8"/>
+    <sheet name="PFCCS" sheetId="24" r:id="rId9"/>
+    <sheet name="FCCS" sheetId="9" r:id="rId10"/>
+    <sheet name="Wed SM Q1" sheetId="5" r:id="rId11"/>
+    <sheet name="Thurs SM Q1" sheetId="7" r:id="rId12"/>
+    <sheet name="Wed SM Q2" sheetId="18" r:id="rId13"/>
+    <sheet name="Thurs SM Q2" sheetId="21" r:id="rId14"/>
+    <sheet name="Wed SM Q3" sheetId="19" r:id="rId15"/>
+    <sheet name="Thurs SM Q3" sheetId="22" r:id="rId16"/>
+    <sheet name="Wed SM Q4" sheetId="20" r:id="rId17"/>
+    <sheet name="Thurs SM Q4" sheetId="23" r:id="rId18"/>
+    <sheet name="STABLE" sheetId="6" r:id="rId19"/>
+    <sheet name="OB Lite" sheetId="10" r:id="rId20"/>
+    <sheet name="OB SIM" sheetId="8" r:id="rId21"/>
+    <sheet name="ATLS" sheetId="17" r:id="rId22"/>
+    <sheet name="Course Dates Reference" sheetId="4" r:id="rId23"/>
+    <sheet name="CCEMT CRM Sched" sheetId="11" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="271">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -865,6 +866,12 @@
   </si>
   <si>
     <t>LT</t>
+  </si>
+  <si>
+    <t>MULTI_SESSION</t>
+  </si>
+  <si>
+    <t>SESSION_LENGTH</t>
   </si>
 </sst>
 </file>
@@ -874,7 +881,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -953,7 +960,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1006,6 +1013,24 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1053,7 +1078,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1655,30 +1680,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE3E758-B252-634C-B9B3-AE34AE7DE6C7}">
   <dimension ref="A1:Y154"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="16.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="16.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="21.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="1" customWidth="1"/>
     <col min="13" max="13" width="9.5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="11.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="15.125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="16.125" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="10.875" style="1"/>
+    <col min="14" max="14" width="12.1640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="15.1640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.95">
+    <row r="1" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1755,7 +1780,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.95">
+    <row r="2" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1829,7 +1854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.95">
+    <row r="3" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1906,7 +1931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.95">
+    <row r="4" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1980,7 +2005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.95">
+    <row r="5" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -2054,7 +2079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.95">
+    <row r="6" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -2128,7 +2153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.95">
+    <row r="7" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -2202,7 +2227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.95">
+    <row r="8" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -2279,7 +2304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.95">
+    <row r="9" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
@@ -2356,7 +2381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.95">
+    <row r="10" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -2430,7 +2455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.95">
+    <row r="11" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -2504,7 +2529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.95">
+    <row r="12" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -2578,7 +2603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.95">
+    <row r="13" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -2652,7 +2677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.95">
+    <row r="14" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -2726,7 +2751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.95">
+    <row r="15" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
@@ -2800,7 +2825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.95">
+    <row r="16" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
@@ -2874,7 +2899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15.95">
+    <row r="17" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -2948,7 +2973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.95">
+    <row r="18" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -3022,7 +3047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.95">
+    <row r="19" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -3096,7 +3121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.95">
+    <row r="20" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -3170,7 +3195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.95">
+    <row r="21" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -3244,7 +3269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.95">
+    <row r="22" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>46</v>
       </c>
@@ -3318,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.95">
+    <row r="23" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>47</v>
       </c>
@@ -3392,7 +3417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.95">
+    <row r="24" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
@@ -3466,7 +3491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.95">
+    <row r="25" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -3540,7 +3565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.95">
+    <row r="26" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -3614,7 +3639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="15.95">
+    <row r="27" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>51</v>
       </c>
@@ -3691,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="15.95">
+    <row r="28" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>52</v>
       </c>
@@ -3765,7 +3790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="15.95">
+    <row r="29" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>53</v>
       </c>
@@ -3839,7 +3864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="15.95">
+    <row r="30" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>54</v>
       </c>
@@ -3913,7 +3938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="15.95">
+    <row r="31" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>55</v>
       </c>
@@ -3987,7 +4012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="15.95">
+    <row r="32" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>56</v>
       </c>
@@ -4061,7 +4086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="15.95">
+    <row r="33" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>57</v>
       </c>
@@ -4135,7 +4160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="15.95">
+    <row r="34" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>58</v>
       </c>
@@ -4209,7 +4234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="15.95">
+    <row r="35" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>59</v>
       </c>
@@ -4283,7 +4308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="15.95">
+    <row r="36" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>60</v>
       </c>
@@ -4357,7 +4382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="15.95">
+    <row r="37" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>61</v>
       </c>
@@ -4434,7 +4459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="15.95">
+    <row r="38" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>62</v>
       </c>
@@ -4508,7 +4533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="15.95">
+    <row r="39" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>63</v>
       </c>
@@ -4582,7 +4607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="15.95">
+    <row r="40" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>64</v>
       </c>
@@ -4659,7 +4684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="15.95">
+    <row r="41" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>65</v>
       </c>
@@ -4733,7 +4758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="15.95">
+    <row r="42" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>66</v>
       </c>
@@ -4807,7 +4832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="15.95">
+    <row r="43" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>67</v>
       </c>
@@ -4884,7 +4909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="15.95">
+    <row r="44" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>69</v>
       </c>
@@ -4958,7 +4983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="15.95">
+    <row r="45" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>70</v>
       </c>
@@ -5032,7 +5057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="15.95">
+    <row r="46" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>71</v>
       </c>
@@ -5106,7 +5131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="15.95">
+    <row r="47" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>72</v>
       </c>
@@ -5180,7 +5205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="15.95">
+    <row r="48" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>73</v>
       </c>
@@ -5254,7 +5279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="15.95">
+    <row r="49" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>74</v>
       </c>
@@ -5328,7 +5353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="15.95">
+    <row r="50" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>75</v>
       </c>
@@ -5402,7 +5427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="15.95">
+    <row r="51" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>76</v>
       </c>
@@ -5479,7 +5504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="15.95">
+    <row r="52" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>77</v>
       </c>
@@ -5553,7 +5578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="15.95">
+    <row r="53" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>78</v>
       </c>
@@ -5630,7 +5655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="15.95">
+    <row r="54" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>79</v>
       </c>
@@ -5704,7 +5729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="15.95">
+    <row r="55" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>80</v>
       </c>
@@ -5781,7 +5806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="15.95">
+    <row r="56" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>81</v>
       </c>
@@ -5858,7 +5883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="15.95">
+    <row r="57" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>82</v>
       </c>
@@ -5932,7 +5957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="15.95">
+    <row r="58" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>83</v>
       </c>
@@ -6006,7 +6031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="15.95">
+    <row r="59" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>84</v>
       </c>
@@ -6080,7 +6105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="15.95">
+    <row r="60" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>85</v>
       </c>
@@ -6157,7 +6182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="15.95">
+    <row r="61" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>86</v>
       </c>
@@ -6231,7 +6256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="15.95">
+    <row r="62" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>87</v>
       </c>
@@ -6308,7 +6333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="15.95">
+    <row r="63" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>88</v>
       </c>
@@ -6382,7 +6407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="15.95">
+    <row r="64" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>89</v>
       </c>
@@ -6456,7 +6481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="15.95">
+    <row r="65" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>90</v>
       </c>
@@ -6530,7 +6555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="15.95">
+    <row r="66" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>91</v>
       </c>
@@ -6604,7 +6629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="15.95">
+    <row r="67" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>92</v>
       </c>
@@ -6678,7 +6703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="15.95">
+    <row r="68" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>93</v>
       </c>
@@ -6752,7 +6777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="15.95">
+    <row r="69" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>94</v>
       </c>
@@ -6829,7 +6854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="15.95">
+    <row r="70" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>95</v>
       </c>
@@ -6903,7 +6928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="15.95">
+    <row r="71" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>96</v>
       </c>
@@ -6977,7 +7002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="15.95">
+    <row r="72" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>97</v>
       </c>
@@ -7051,7 +7076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="15.95">
+    <row r="73" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>98</v>
       </c>
@@ -7125,7 +7150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="15.95">
+    <row r="74" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>99</v>
       </c>
@@ -7202,7 +7227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="15.95">
+    <row r="75" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>100</v>
       </c>
@@ -7276,7 +7301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="15.95">
+    <row r="76" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>101</v>
       </c>
@@ -7350,7 +7375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="15.95">
+    <row r="77" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>102</v>
       </c>
@@ -7424,7 +7449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="15.95">
+    <row r="78" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>103</v>
       </c>
@@ -7498,7 +7523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="15.95">
+    <row r="79" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>104</v>
       </c>
@@ -7572,7 +7597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="15.95">
+    <row r="80" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>105</v>
       </c>
@@ -7646,7 +7671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="15.95">
+    <row r="81" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>106</v>
       </c>
@@ -7717,7 +7742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="15.95">
+    <row r="82" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>107</v>
       </c>
@@ -7746,7 +7771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="15.95">
+    <row r="83" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>109</v>
       </c>
@@ -7775,7 +7800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="15.95">
+    <row r="84" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>110</v>
       </c>
@@ -7804,7 +7829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="15.95">
+    <row r="85" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>111</v>
       </c>
@@ -7833,7 +7858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="15.95">
+    <row r="86" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>112</v>
       </c>
@@ -7862,7 +7887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="15.95">
+    <row r="87" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>113</v>
       </c>
@@ -7891,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="15.95">
+    <row r="88" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>114</v>
       </c>
@@ -7920,7 +7945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="15.95">
+    <row r="89" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>115</v>
       </c>
@@ -7949,7 +7974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="15.95">
+    <row r="90" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>116</v>
       </c>
@@ -7978,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="15.95">
+    <row r="91" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>117</v>
       </c>
@@ -8007,7 +8032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="15.95">
+    <row r="92" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>118</v>
       </c>
@@ -8036,7 +8061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="15.95">
+    <row r="93" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>119</v>
       </c>
@@ -8065,7 +8090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="15.95">
+    <row r="94" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>120</v>
       </c>
@@ -8094,7 +8119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="15.95">
+    <row r="95" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>121</v>
       </c>
@@ -8123,7 +8148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="15.95">
+    <row r="96" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>122</v>
       </c>
@@ -8152,7 +8177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="15.95">
+    <row r="97" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>123</v>
       </c>
@@ -8181,7 +8206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="15.95">
+    <row r="98" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>124</v>
       </c>
@@ -8213,7 +8238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="15.95">
+    <row r="99" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>126</v>
       </c>
@@ -8245,7 +8270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="15.95">
+    <row r="100" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>127</v>
       </c>
@@ -8277,7 +8302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="15.95">
+    <row r="101" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>128</v>
       </c>
@@ -8309,7 +8334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="15.95">
+    <row r="102" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>129</v>
       </c>
@@ -8341,7 +8366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="15.95">
+    <row r="103" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>130</v>
       </c>
@@ -8373,7 +8398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="15.95">
+    <row r="104" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>131</v>
       </c>
@@ -8414,7 +8439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="15.95">
+    <row r="105" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>132</v>
       </c>
@@ -8446,7 +8471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="15.95">
+    <row r="106" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>133</v>
       </c>
@@ -8478,7 +8503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="15.95">
+    <row r="107" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>134</v>
       </c>
@@ -8510,7 +8535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="15.95">
+    <row r="108" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>135</v>
       </c>
@@ -8542,7 +8567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="15.95">
+    <row r="109" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>136</v>
       </c>
@@ -8574,7 +8599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="15.95">
+    <row r="110" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>137</v>
       </c>
@@ -8606,7 +8631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="15.95">
+    <row r="111" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>138</v>
       </c>
@@ -8638,7 +8663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="15.95">
+    <row r="112" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>139</v>
       </c>
@@ -8670,7 +8695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="15.95">
+    <row r="113" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>140</v>
       </c>
@@ -8702,7 +8727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="15.95">
+    <row r="114" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>141</v>
       </c>
@@ -8734,7 +8759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="15.95">
+    <row r="115" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>142</v>
       </c>
@@ -8766,7 +8791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="15.95">
+    <row r="116" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>143</v>
       </c>
@@ -8795,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="15.95">
+    <row r="117" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>145</v>
       </c>
@@ -8824,7 +8849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="15.95">
+    <row r="118" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>146</v>
       </c>
@@ -8853,7 +8878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="15.95">
+    <row r="119" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>147</v>
       </c>
@@ -8882,7 +8907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="15.95">
+    <row r="120" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>148</v>
       </c>
@@ -8911,7 +8936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="15.95">
+    <row r="121" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>149</v>
       </c>
@@ -8940,7 +8965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="15.95">
+    <row r="122" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>150</v>
       </c>
@@ -8969,7 +8994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="15.95">
+    <row r="123" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>151</v>
       </c>
@@ -8998,7 +9023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="15.95">
+    <row r="124" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>152</v>
       </c>
@@ -9027,7 +9052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="15.95">
+    <row r="125" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>153</v>
       </c>
@@ -9056,7 +9081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="15.95">
+    <row r="126" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>154</v>
       </c>
@@ -9085,7 +9110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="15.95">
+    <row r="127" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>155</v>
       </c>
@@ -9114,7 +9139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="15.95">
+    <row r="128" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>156</v>
       </c>
@@ -9143,7 +9168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="15.75" customHeight="1">
+    <row r="129" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>157</v>
       </c>
@@ -9172,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="15.75" customHeight="1">
+    <row r="130" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>158</v>
       </c>
@@ -9201,7 +9226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="15.75" customHeight="1">
+    <row r="131" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>159</v>
       </c>
@@ -9230,7 +9255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="15.75" customHeight="1">
+    <row r="132" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>160</v>
       </c>
@@ -9259,7 +9284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="15.75" customHeight="1">
+    <row r="133" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>161</v>
       </c>
@@ -9288,7 +9313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="15.75" customHeight="1">
+    <row r="134" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>162</v>
       </c>
@@ -9317,7 +9342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="15.75" customHeight="1">
+    <row r="135" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>163</v>
       </c>
@@ -9346,7 +9371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="15.75" customHeight="1">
+    <row r="136" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>164</v>
       </c>
@@ -9375,7 +9400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="15.75" customHeight="1">
+    <row r="137" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>165</v>
       </c>
@@ -9404,7 +9429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="15.75" customHeight="1">
+    <row r="138" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>166</v>
       </c>
@@ -9433,7 +9458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="15.75" customHeight="1">
+    <row r="139" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>167</v>
       </c>
@@ -9462,7 +9487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="15.75" customHeight="1">
+    <row r="140" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>168</v>
       </c>
@@ -9491,7 +9516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="15.75" customHeight="1">
+    <row r="141" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>169</v>
       </c>
@@ -9520,7 +9545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="15.75" customHeight="1">
+    <row r="142" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>170</v>
       </c>
@@ -9549,7 +9574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="15.75" customHeight="1">
+    <row r="143" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>172</v>
       </c>
@@ -9578,7 +9603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="15.75" customHeight="1">
+    <row r="144" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>173</v>
       </c>
@@ -9607,7 +9632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="15.75" customHeight="1">
+    <row r="145" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>174</v>
       </c>
@@ -9636,7 +9661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="15.75" customHeight="1">
+    <row r="146" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>175</v>
       </c>
@@ -9665,7 +9690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="15.75" customHeight="1">
+    <row r="147" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>176</v>
       </c>
@@ -9694,7 +9719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="15.75" customHeight="1">
+    <row r="148" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>177</v>
       </c>
@@ -9723,7 +9748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="15.75" customHeight="1">
+    <row r="149" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>178</v>
       </c>
@@ -9752,7 +9777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="15.75" customHeight="1">
+    <row r="150" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>179</v>
       </c>
@@ -9781,7 +9806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="15.75" customHeight="1">
+    <row r="151" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>180</v>
       </c>
@@ -9810,7 +9835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="15.75" customHeight="1">
+    <row r="152" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>181</v>
       </c>
@@ -9839,7 +9864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="15.75" customHeight="1">
+    <row r="153" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>182</v>
       </c>
@@ -9868,7 +9893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="15.75" customHeight="1">
+    <row r="154" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>183</v>
       </c>
@@ -9906,17 +9931,311 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8307E2-C15E-3246-97E6-1FE53EC08157}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="6">
+        <v>45936</v>
+      </c>
+      <c r="C1" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D1" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="6">
+        <v>46118</v>
+      </c>
+      <c r="C2" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C15" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="11">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B28" s="3">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17 B19" xr:uid="{3D6AA655-0937-D041-BAA2-9AD8C4D94C09}">
+      <formula1>"Yes, No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58626D5E-CF7D-7040-8A8E-EE19354196C8}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.875" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="2" max="3" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -9930,7 +10249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -9944,7 +10263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -9958,7 +10277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -9969,7 +10288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -9980,7 +10299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -9991,7 +10310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -10002,7 +10321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -10013,7 +10332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -10025,7 +10344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -10037,7 +10356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -10049,7 +10368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -10061,7 +10380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -10073,7 +10392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -10085,7 +10404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -10096,7 +10415,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -10104,7 +10423,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -10112,7 +10431,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -10120,7 +10439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -10128,7 +10447,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -10136,7 +10455,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -10144,37 +10463,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -10192,18 +10511,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9BC729-92D2-4067-85BC-DFDCD994C98C}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.875" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="2" max="3" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -10217,7 +10536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -10231,7 +10550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -10245,7 +10564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -10256,7 +10575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -10267,7 +10586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -10278,7 +10597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -10289,7 +10608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -10300,7 +10619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -10312,7 +10631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -10324,7 +10643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -10336,7 +10655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -10348,7 +10667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -10360,7 +10679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -10372,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -10383,7 +10702,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -10391,7 +10710,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -10399,7 +10718,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -10407,7 +10726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -10415,7 +10734,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -10423,7 +10742,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -10431,37 +10750,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -10479,18 +10798,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D88D2FE4-23CC-491D-BD62-D960817AB0D2}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -10504,7 +10823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -10518,7 +10837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -10532,7 +10851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -10543,7 +10862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -10554,7 +10873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -10565,7 +10884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -10576,7 +10895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -10587,7 +10906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -10599,7 +10918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -10611,7 +10930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -10623,7 +10942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -10635,7 +10954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -10647,7 +10966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -10659,7 +10978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -10670,7 +10989,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -10678,7 +10997,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -10686,7 +11005,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -10694,7 +11013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -10702,7 +11021,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -10710,7 +11029,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -10718,37 +11037,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -10766,19 +11085,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24407AE7-238F-42BD-B8EA-6F88E165DF83}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -10792,7 +11111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -10806,7 +11125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -10820,7 +11139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -10831,7 +11150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -10842,7 +11161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -10853,7 +11172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -10864,7 +11183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -10875,7 +11194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -10887,7 +11206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -10899,7 +11218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -10911,7 +11230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -10923,7 +11242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -10935,7 +11254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -10947,7 +11266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -10958,7 +11277,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -10966,7 +11285,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -10974,7 +11293,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -10982,7 +11301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -10990,7 +11309,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -10998,7 +11317,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -11006,37 +11325,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -11054,18 +11373,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7578FEE-5B85-43AD-81EE-212BA4C5295B}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -11079,7 +11398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -11093,7 +11412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -11107,7 +11426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -11118,7 +11437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -11129,7 +11448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -11140,7 +11459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -11151,7 +11470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -11162,7 +11481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -11174,7 +11493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -11186,7 +11505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -11198,7 +11517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -11210,7 +11529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -11222,7 +11541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -11234,7 +11553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -11245,7 +11564,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -11253,7 +11572,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -11261,7 +11580,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -11269,7 +11588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -11277,7 +11596,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -11285,7 +11604,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -11293,37 +11612,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -11341,19 +11660,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CEAB94E-7986-48ED-9C86-1B1BBA3C1E49}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -11367,7 +11686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -11381,7 +11700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -11395,7 +11714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -11406,7 +11725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -11417,7 +11736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -11428,7 +11747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -11439,7 +11758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -11450,7 +11769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -11462,7 +11781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -11474,7 +11793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -11486,7 +11805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -11498,7 +11817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -11510,7 +11829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -11522,7 +11841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -11533,7 +11852,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -11541,7 +11860,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -11549,7 +11868,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -11557,7 +11876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -11565,7 +11884,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -11573,7 +11892,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -11581,37 +11900,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -11629,18 +11948,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC058F5-09C7-4162-863E-422D32EBC74A}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -11654,7 +11973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -11668,7 +11987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -11682,7 +12001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -11693,7 +12012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -11704,7 +12023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -11715,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -11726,7 +12045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -11737,7 +12056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -11749,7 +12068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -11761,7 +12080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -11773,7 +12092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -11785,7 +12104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -11797,7 +12116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -11809,7 +12128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -11820,7 +12139,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -11828,7 +12147,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -11836,7 +12155,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -11844,7 +12163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -11852,7 +12171,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -11860,7 +12179,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -11868,37 +12187,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -11916,19 +12235,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFE2395-82E7-4A11-91BF-FB62274BB4C3}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -11942,7 +12261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -11956,7 +12275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -11970,7 +12289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -11981,7 +12300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -11992,7 +12311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -12003,7 +12322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -12014,7 +12333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -12025,7 +12344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -12037,7 +12356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -12049,7 +12368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -12061,7 +12380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -12073,7 +12392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -12085,7 +12404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -12097,7 +12416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -12108,7 +12427,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -12116,7 +12435,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -12124,7 +12443,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -12132,7 +12451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -12140,7 +12459,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -12148,7 +12467,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -12156,37 +12475,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -12204,18 +12523,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{251C4556-B6F5-4EAB-AE0D-DC7FA135F386}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.875" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="2" max="3" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -12232,7 +12551,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -12249,7 +12568,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -12266,7 +12585,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -12283,7 +12602,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -12300,7 +12619,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -12317,7 +12636,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -12334,7 +12653,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -12351,7 +12670,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -12363,7 +12682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -12375,7 +12694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -12387,7 +12706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -12399,7 +12718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -12411,7 +12730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -12423,7 +12742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -12434,7 +12753,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -12442,7 +12761,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -12450,7 +12769,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -12458,7 +12777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -12466,7 +12785,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -12474,7 +12793,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -12482,37 +12801,37 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -12530,319 +12849,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73369AC4-C9B4-42DD-BF9C-2665EDC8C92A}">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
-  <cols>
-    <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="8">
-        <v>46042</v>
-      </c>
-      <c r="C1" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D1" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B2" s="8">
-        <v>46104</v>
-      </c>
-      <c r="C2" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="C15" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B16" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B20" s="11">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="11">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B22" s="11"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B23" s="11"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B24" s="11"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B25" s="11"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B28" s="3">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17 B19" xr:uid="{F49EE81B-1567-468D-8A98-C2779CCC831D}">
-      <formula1>"Yes, No"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD174F3-4421-40E9-ADA5-4D51B58F838B}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.875" style="3"/>
+    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -12859,7 +12878,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -12876,7 +12895,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -12893,7 +12912,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -12910,7 +12929,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -12927,7 +12946,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -12944,7 +12963,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -12961,7 +12980,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -12978,7 +12997,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -12995,7 +13014,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -13012,7 +13031,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -13029,7 +13048,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -13046,7 +13065,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -13063,7 +13082,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -13075,7 +13094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -13086,7 +13105,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -13094,7 +13113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -13102,7 +13121,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -13110,7 +13129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -13118,7 +13137,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -13126,7 +13145,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -13134,7 +13153,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
@@ -13142,7 +13161,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
@@ -13150,7 +13169,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
@@ -13158,7 +13177,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
@@ -13166,17 +13185,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -13195,17 +13214,317 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73369AC4-C9B4-42DD-BF9C-2665EDC8C92A}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="8">
+        <v>46042</v>
+      </c>
+      <c r="C1" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D1" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="8">
+        <v>46104</v>
+      </c>
+      <c r="C2" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C15" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="11">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="11"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" s="11"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" s="11"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" s="11"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17 B19" xr:uid="{F49EE81B-1567-468D-8A98-C2779CCC831D}">
+      <formula1>"Yes, No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DEE273-7DC8-284A-9883-269CFB150B79}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.875" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="2" max="3" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -13222,7 +13541,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -13239,7 +13558,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -13256,7 +13575,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -13273,7 +13592,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -13290,7 +13609,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -13307,7 +13626,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -13324,7 +13643,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -13335,7 +13654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -13347,7 +13666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -13359,7 +13678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -13371,7 +13690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -13383,7 +13702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -13395,7 +13714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -13407,7 +13726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -13418,7 +13737,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -13426,7 +13745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -13434,7 +13753,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -13442,7 +13761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -13450,7 +13769,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -13458,7 +13777,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -13466,7 +13785,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
@@ -13474,7 +13793,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
@@ -13482,7 +13801,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
@@ -13490,7 +13809,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
@@ -13498,17 +13817,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -13526,20 +13845,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0587D0-89DF-4D05-A902-12BFC82DD3EC}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.875" style="3"/>
+    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -13556,7 +13875,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -13573,7 +13892,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -13590,7 +13909,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -13607,7 +13926,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -13624,7 +13943,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -13641,7 +13960,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -13658,7 +13977,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -13675,7 +13994,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -13692,7 +14011,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -13709,7 +14028,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -13726,7 +14045,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -13743,7 +14062,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -13760,7 +14079,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -13777,7 +14096,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -13788,7 +14107,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -13796,7 +14115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -13804,7 +14123,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -13812,7 +14131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -13820,7 +14139,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -13828,7 +14147,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -13836,41 +14155,41 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -13888,16 +14207,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D7DB1A-8C06-5D43-8D41-553EA9E8A37B}">
   <dimension ref="A1:N99"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="8" max="8" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>224</v>
       </c>
@@ -13941,7 +14260,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>231</v>
       </c>
@@ -13971,7 +14290,7 @@
       </c>
       <c r="J2" s="16"/>
     </row>
-    <row r="3" spans="1:14" hidden="1">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>236</v>
@@ -13993,7 +14312,7 @@
       </c>
       <c r="J3" s="16"/>
     </row>
-    <row r="4" spans="1:14" hidden="1">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="E4" s="6">
         <v>46063</v>
@@ -14009,7 +14328,7 @@
       </c>
       <c r="J4" s="16"/>
     </row>
-    <row r="5" spans="1:14" hidden="1">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="E5" s="6">
         <v>46091</v>
@@ -14027,7 +14346,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="E6" s="6">
         <v>46114</v>
@@ -14043,7 +14362,7 @@
       </c>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:14" hidden="1">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="E7" s="6">
         <v>46170</v>
@@ -14059,7 +14378,7 @@
       </c>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:14" hidden="1">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="F8" s="8">
         <v>46294</v>
@@ -14072,7 +14391,7 @@
       </c>
       <c r="J8" s="16"/>
     </row>
-    <row r="9" spans="1:14" hidden="1">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H9" s="16" t="s">
         <v>235</v>
       </c>
@@ -14083,7 +14402,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H10" s="16" t="s">
         <v>235</v>
       </c>
@@ -14092,7 +14411,7 @@
       </c>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:14" hidden="1">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H11" s="16" t="s">
         <v>235</v>
       </c>
@@ -14101,7 +14420,7 @@
       </c>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:14" hidden="1">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="H12" s="16" t="s">
         <v>235</v>
@@ -14111,7 +14430,7 @@
       </c>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:14" hidden="1">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="H13" s="16" t="s">
         <v>235</v>
@@ -14123,7 +14442,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="H14" s="16" t="s">
         <v>239</v>
@@ -14133,7 +14452,7 @@
       </c>
       <c r="J14" s="16"/>
     </row>
-    <row r="15" spans="1:14" hidden="1">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="H15" s="16" t="s">
         <v>239</v>
@@ -14145,7 +14464,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="16" spans="1:14" hidden="1">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="H16" s="16" t="s">
         <v>239</v>
@@ -14155,7 +14474,7 @@
       </c>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" spans="1:10" hidden="1">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H17" s="16" t="s">
         <v>239</v>
       </c>
@@ -14164,7 +14483,7 @@
       </c>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" spans="1:10" hidden="1">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H18" s="16" t="s">
         <v>239</v>
       </c>
@@ -14173,7 +14492,7 @@
       </c>
       <c r="J18" s="16"/>
     </row>
-    <row r="19" spans="1:10" hidden="1">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H19" s="16" t="s">
         <v>239</v>
       </c>
@@ -14184,7 +14503,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="H20" s="16" t="s">
         <v>239</v>
@@ -14194,7 +14513,7 @@
       </c>
       <c r="J20" s="16"/>
     </row>
-    <row r="21" spans="1:10" hidden="1">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="H21" s="16" t="s">
         <v>239</v>
@@ -14204,7 +14523,7 @@
       </c>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" spans="1:10" hidden="1">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="H22" s="16" t="s">
         <v>239</v>
@@ -14214,7 +14533,7 @@
       </c>
       <c r="J22" s="16"/>
     </row>
-    <row r="23" spans="1:10" hidden="1">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="H23" s="16" t="s">
         <v>239</v>
@@ -14226,7 +14545,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="H24" s="16" t="s">
         <v>239</v>
@@ -14236,7 +14555,7 @@
       </c>
       <c r="J24" s="16"/>
     </row>
-    <row r="25" spans="1:10" hidden="1">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H25" s="16" t="s">
         <v>239</v>
       </c>
@@ -14245,7 +14564,7 @@
       </c>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" spans="1:10" hidden="1">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H26" s="16" t="s">
         <v>240</v>
       </c>
@@ -14254,7 +14573,7 @@
       </c>
       <c r="J26" s="16"/>
     </row>
-    <row r="27" spans="1:10" hidden="1">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="H27" s="16" t="s">
         <v>240</v>
@@ -14264,7 +14583,7 @@
       </c>
       <c r="J27" s="16"/>
     </row>
-    <row r="28" spans="1:10" hidden="1">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="H28" s="16" t="s">
         <v>240</v>
@@ -14274,7 +14593,7 @@
       </c>
       <c r="J28" s="16"/>
     </row>
-    <row r="29" spans="1:10" hidden="1">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
       <c r="H29" s="16" t="s">
         <v>240</v>
@@ -14284,7 +14603,7 @@
       </c>
       <c r="J29" s="16"/>
     </row>
-    <row r="30" spans="1:10" hidden="1">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
       <c r="H30" s="16" t="s">
         <v>240</v>
@@ -14294,7 +14613,7 @@
       </c>
       <c r="J30" s="16"/>
     </row>
-    <row r="31" spans="1:10" hidden="1">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="H31" s="16" t="s">
         <v>240</v>
@@ -14304,7 +14623,7 @@
       </c>
       <c r="J31" s="16"/>
     </row>
-    <row r="32" spans="1:10" hidden="1">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
       <c r="H32" s="16" t="s">
         <v>240</v>
@@ -14314,7 +14633,7 @@
       </c>
       <c r="J32" s="16"/>
     </row>
-    <row r="33" spans="1:10" hidden="1">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H33" s="16" t="s">
         <v>241</v>
       </c>
@@ -14323,7 +14642,7 @@
       </c>
       <c r="J33" s="16"/>
     </row>
-    <row r="34" spans="1:10" hidden="1">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H34" s="16" t="s">
         <v>241</v>
       </c>
@@ -14332,7 +14651,7 @@
       </c>
       <c r="J34" s="16"/>
     </row>
-    <row r="35" spans="1:10" hidden="1">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H35" s="16" t="s">
         <v>241</v>
       </c>
@@ -14341,7 +14660,7 @@
       </c>
       <c r="J35" s="16"/>
     </row>
-    <row r="36" spans="1:10" hidden="1">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H36" s="16" t="s">
         <v>241</v>
       </c>
@@ -14350,7 +14669,7 @@
       </c>
       <c r="J36" s="16"/>
     </row>
-    <row r="37" spans="1:10" hidden="1">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H37" s="16" t="s">
         <v>241</v>
       </c>
@@ -14359,7 +14678,7 @@
       </c>
       <c r="J37" s="16"/>
     </row>
-    <row r="38" spans="1:10" hidden="1">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H38" s="16" t="s">
         <v>241</v>
       </c>
@@ -14368,7 +14687,7 @@
       </c>
       <c r="J38" s="16"/>
     </row>
-    <row r="39" spans="1:10" hidden="1">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H39" s="16" t="s">
         <v>241</v>
       </c>
@@ -14377,7 +14696,7 @@
       </c>
       <c r="J39" s="16"/>
     </row>
-    <row r="40" spans="1:10" hidden="1">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
       <c r="H40" s="16" t="s">
         <v>241</v>
@@ -14387,7 +14706,7 @@
       </c>
       <c r="J40" s="16"/>
     </row>
-    <row r="41" spans="1:10" hidden="1">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>15</v>
       </c>
@@ -14399,7 +14718,7 @@
       </c>
       <c r="J41" s="16"/>
     </row>
-    <row r="42" spans="1:10" hidden="1">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>46253</v>
       </c>
@@ -14411,7 +14730,7 @@
       </c>
       <c r="J42" s="16"/>
     </row>
-    <row r="43" spans="1:10" hidden="1">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>46260</v>
       </c>
@@ -14425,7 +14744,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>46266</v>
       </c>
@@ -14439,7 +14758,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>46274</v>
       </c>
@@ -14453,7 +14772,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>46280</v>
       </c>
@@ -14465,7 +14784,7 @@
       </c>
       <c r="J46" s="16"/>
     </row>
-    <row r="47" spans="1:10" hidden="1">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>46288</v>
       </c>
@@ -14477,7 +14796,7 @@
       </c>
       <c r="J47" s="16"/>
     </row>
-    <row r="48" spans="1:10" hidden="1">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>46294</v>
       </c>
@@ -14489,7 +14808,7 @@
       </c>
       <c r="J48" s="16"/>
     </row>
-    <row r="49" spans="1:10" hidden="1">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>16</v>
       </c>
@@ -14501,7 +14820,7 @@
       </c>
       <c r="J49" s="16"/>
     </row>
-    <row r="50" spans="1:10" hidden="1">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>234</v>
       </c>
@@ -14513,7 +14832,7 @@
       </c>
       <c r="J50" s="16"/>
     </row>
-    <row r="51" spans="1:10" hidden="1">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5"/>
       <c r="H51" s="16" t="s">
         <v>243</v>
@@ -14523,7 +14842,7 @@
       </c>
       <c r="J51" s="16"/>
     </row>
-    <row r="52" spans="1:10" hidden="1">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5"/>
       <c r="H52" s="16" t="s">
         <v>243</v>
@@ -14533,7 +14852,7 @@
       </c>
       <c r="J52" s="16"/>
     </row>
-    <row r="53" spans="1:10" hidden="1">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5"/>
       <c r="H53" s="16" t="s">
         <v>243</v>
@@ -14543,7 +14862,7 @@
       </c>
       <c r="J53" s="16"/>
     </row>
-    <row r="54" spans="1:10" hidden="1">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5"/>
       <c r="H54" s="16" t="s">
         <v>243</v>
@@ -14553,7 +14872,7 @@
       </c>
       <c r="J54" s="16"/>
     </row>
-    <row r="55" spans="1:10" hidden="1">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="H55" s="16" t="s">
         <v>243</v>
@@ -14563,7 +14882,7 @@
       </c>
       <c r="J55" s="16"/>
     </row>
-    <row r="56" spans="1:10" hidden="1">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="H56" s="16" t="s">
         <v>243</v>
@@ -14573,7 +14892,7 @@
       </c>
       <c r="J56" s="16"/>
     </row>
-    <row r="57" spans="1:10" hidden="1">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H57" s="16" t="s">
         <v>243</v>
       </c>
@@ -14582,7 +14901,7 @@
       </c>
       <c r="J57" s="16"/>
     </row>
-    <row r="58" spans="1:10" hidden="1">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H58" s="16" t="s">
         <v>244</v>
       </c>
@@ -14591,7 +14910,7 @@
       </c>
       <c r="J58" s="16"/>
     </row>
-    <row r="59" spans="1:10" hidden="1">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H59" s="16" t="s">
         <v>244</v>
       </c>
@@ -14600,7 +14919,7 @@
       </c>
       <c r="J59" s="16"/>
     </row>
-    <row r="60" spans="1:10" hidden="1">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H60" s="16" t="s">
         <v>244</v>
       </c>
@@ -14609,7 +14928,7 @@
       </c>
       <c r="J60" s="16"/>
     </row>
-    <row r="61" spans="1:10" hidden="1">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H61" s="16" t="s">
         <v>244</v>
       </c>
@@ -14618,7 +14937,7 @@
       </c>
       <c r="J61" s="16"/>
     </row>
-    <row r="62" spans="1:10" hidden="1">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H62" s="16" t="s">
         <v>244</v>
       </c>
@@ -14627,7 +14946,7 @@
       </c>
       <c r="J62" s="16"/>
     </row>
-    <row r="63" spans="1:10" hidden="1">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H63" s="16" t="s">
         <v>244</v>
       </c>
@@ -14636,7 +14955,7 @@
       </c>
       <c r="J63" s="16"/>
     </row>
-    <row r="64" spans="1:10" hidden="1">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H64" s="16" t="s">
         <v>244</v>
       </c>
@@ -14645,7 +14964,7 @@
       </c>
       <c r="J64" s="16"/>
     </row>
-    <row r="65" spans="8:14" hidden="1">
+    <row r="65" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H65" s="16" t="s">
         <v>244</v>
       </c>
@@ -14654,7 +14973,7 @@
       </c>
       <c r="J65" s="16"/>
     </row>
-    <row r="66" spans="8:14" hidden="1">
+    <row r="66" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H66" s="16" t="s">
         <v>244</v>
       </c>
@@ -14663,7 +14982,7 @@
       </c>
       <c r="J66" s="16"/>
     </row>
-    <row r="67" spans="8:14" hidden="1">
+    <row r="67" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H67" s="16" t="s">
         <v>244</v>
       </c>
@@ -14672,7 +14991,7 @@
       </c>
       <c r="J67" s="16"/>
     </row>
-    <row r="68" spans="8:14" hidden="1">
+    <row r="68" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H68" s="16" t="s">
         <v>244</v>
       </c>
@@ -14683,7 +15002,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="69" spans="8:14" hidden="1">
+    <row r="69" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H69" s="16" t="s">
         <v>244</v>
       </c>
@@ -14694,7 +15013,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="70" spans="8:14" hidden="1">
+    <row r="70" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H70" s="16" t="s">
         <v>244</v>
       </c>
@@ -14705,7 +15024,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="71" spans="8:14" hidden="1">
+    <row r="71" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H71" s="16" t="s">
         <v>246</v>
       </c>
@@ -14714,7 +15033,7 @@
       </c>
       <c r="J71" s="16"/>
     </row>
-    <row r="72" spans="8:14" hidden="1">
+    <row r="72" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H72" s="16" t="s">
         <v>246</v>
       </c>
@@ -14723,7 +15042,7 @@
       </c>
       <c r="J72" s="16"/>
     </row>
-    <row r="73" spans="8:14" hidden="1">
+    <row r="73" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H73" s="16" t="s">
         <v>246</v>
       </c>
@@ -14732,7 +15051,7 @@
       </c>
       <c r="J73" s="16"/>
     </row>
-    <row r="74" spans="8:14" hidden="1">
+    <row r="74" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H74" s="16" t="s">
         <v>246</v>
       </c>
@@ -14741,7 +15060,7 @@
       </c>
       <c r="J74" s="16"/>
     </row>
-    <row r="75" spans="8:14" hidden="1">
+    <row r="75" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H75" s="16" t="s">
         <v>246</v>
       </c>
@@ -14750,7 +15069,7 @@
       </c>
       <c r="J75" s="16"/>
     </row>
-    <row r="76" spans="8:14" hidden="1">
+    <row r="76" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H76" s="16" t="s">
         <v>246</v>
       </c>
@@ -14759,7 +15078,7 @@
       </c>
       <c r="J76" s="16"/>
     </row>
-    <row r="77" spans="8:14" hidden="1">
+    <row r="77" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H77" s="16" t="s">
         <v>246</v>
       </c>
@@ -14768,7 +15087,7 @@
       </c>
       <c r="J77" s="16"/>
     </row>
-    <row r="78" spans="8:14" hidden="1">
+    <row r="78" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H78" s="16" t="s">
         <v>247</v>
       </c>
@@ -14785,7 +15104,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="16"/>
     </row>
-    <row r="79" spans="8:14" hidden="1">
+    <row r="79" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H79" s="16" t="s">
         <v>248</v>
       </c>
@@ -14802,7 +15121,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="16"/>
     </row>
-    <row r="80" spans="8:14" hidden="1">
+    <row r="80" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H80" s="16" t="s">
         <v>249</v>
       </c>
@@ -14819,7 +15138,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="16"/>
     </row>
-    <row r="81" spans="8:14" hidden="1">
+    <row r="81" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H81" s="16" t="s">
         <v>250</v>
       </c>
@@ -14830,7 +15149,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="16"/>
     </row>
-    <row r="82" spans="8:14" hidden="1">
+    <row r="82" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H82" s="16" t="s">
         <v>10</v>
       </c>
@@ -14843,7 +15162,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="16"/>
     </row>
-    <row r="83" spans="8:14" hidden="1">
+    <row r="83" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H83" s="16" t="s">
         <v>10</v>
       </c>
@@ -14856,7 +15175,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="16"/>
     </row>
-    <row r="84" spans="8:14">
+    <row r="84" spans="8:14" x14ac:dyDescent="0.2">
       <c r="H84" s="16" t="s">
         <v>11</v>
       </c>
@@ -14869,7 +15188,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="16"/>
     </row>
-    <row r="85" spans="8:14">
+    <row r="85" spans="8:14" x14ac:dyDescent="0.2">
       <c r="H85" s="16" t="s">
         <v>11</v>
       </c>
@@ -14882,7 +15201,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="16"/>
     </row>
-    <row r="86" spans="8:14" hidden="1">
+    <row r="86" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H86" s="16" t="s">
         <v>255</v>
       </c>
@@ -14895,7 +15214,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="16"/>
     </row>
-    <row r="87" spans="8:14" hidden="1">
+    <row r="87" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H87" s="16" t="s">
         <v>255</v>
       </c>
@@ -14908,7 +15227,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="16"/>
     </row>
-    <row r="88" spans="8:14" hidden="1">
+    <row r="88" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H88" s="16" t="s">
         <v>13</v>
       </c>
@@ -14921,7 +15240,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="16"/>
     </row>
-    <row r="89" spans="8:14" hidden="1">
+    <row r="89" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H89" s="16" t="s">
         <v>13</v>
       </c>
@@ -14934,7 +15253,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="16"/>
     </row>
-    <row r="90" spans="8:14" hidden="1">
+    <row r="90" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H90" s="16" t="s">
         <v>13</v>
       </c>
@@ -14947,7 +15266,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="16"/>
     </row>
-    <row r="91" spans="8:14" hidden="1">
+    <row r="91" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H91" s="16" t="s">
         <v>13</v>
       </c>
@@ -14960,7 +15279,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="16"/>
     </row>
-    <row r="92" spans="8:14" hidden="1">
+    <row r="92" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H92" s="16" t="s">
         <v>13</v>
       </c>
@@ -14973,7 +15292,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="16"/>
     </row>
-    <row r="93" spans="8:14" hidden="1">
+    <row r="93" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H93" s="16" t="s">
         <v>13</v>
       </c>
@@ -14986,7 +15305,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="16"/>
     </row>
-    <row r="94" spans="8:14" hidden="1">
+    <row r="94" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H94" s="16" t="s">
         <v>256</v>
       </c>
@@ -15009,7 +15328,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" spans="8:14" hidden="1">
+    <row r="95" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H95" s="16" t="s">
         <v>258</v>
       </c>
@@ -15032,7 +15351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="96" spans="8:14" hidden="1">
+    <row r="96" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="H96" s="16" t="s">
         <v>259</v>
       </c>
@@ -15055,7 +15374,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="8:10" hidden="1">
+    <row r="97" spans="8:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H97" s="16" t="s">
         <v>261</v>
       </c>
@@ -15064,7 +15383,7 @@
       </c>
       <c r="J97" s="16"/>
     </row>
-    <row r="98" spans="8:10" hidden="1">
+    <row r="98" spans="8:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H98" s="16" t="s">
         <v>262</v>
       </c>
@@ -15073,7 +15392,7 @@
       </c>
       <c r="J98" s="16"/>
     </row>
-    <row r="99" spans="8:10" hidden="1">
+    <row r="99" spans="8:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="H99" s="16" t="s">
         <v>263</v>
       </c>
@@ -15090,16 +15409,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE5E83A-B444-4206-8DA8-1368EF05AF5C}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="13" customFormat="1">
+    <row r="1" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B1" s="13">
         <v>45957</v>
       </c>
@@ -15124,7 +15443,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>124</v>
       </c>
@@ -15147,7 +15466,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -15170,7 +15489,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -15193,7 +15512,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -15216,7 +15535,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -15239,7 +15558,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -15262,7 +15581,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>267</v>
       </c>
@@ -15285,7 +15604,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>131</v>
       </c>
@@ -15308,7 +15627,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -15331,7 +15650,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -15354,7 +15673,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -15377,7 +15696,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -15400,7 +15719,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -15423,7 +15742,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -15446,7 +15765,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -15469,7 +15788,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -15492,7 +15811,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>141</v>
       </c>
@@ -15515,7 +15834,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>142</v>
       </c>
@@ -15544,18 +15863,353 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09EEA88E-7AEE-574F-BC90-87FF2ABA87C3}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="20">
+        <v>46189</v>
+      </c>
+      <c r="C1" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="20">
+        <v>46219</v>
+      </c>
+      <c r="C2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="20">
+        <v>46267</v>
+      </c>
+      <c r="C3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="20">
+        <v>46239</v>
+      </c>
+      <c r="C4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="20">
+        <v>46254</v>
+      </c>
+      <c r="C5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C15" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="25">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="25">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="25"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" s="25"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" s="25"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B25" s="25"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17 B19" xr:uid="{D7006C4C-0587-4C4B-B251-ADE0D8B3D3DF}">
+      <formula1>"Yes, No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D169A3-4EB4-4BAF-ABF2-90D52870D9B1}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.875" style="3"/>
+    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -15575,7 +16229,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -15595,7 +16249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -15612,7 +16266,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -15629,7 +16283,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -15646,7 +16300,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -15663,7 +16317,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -15680,7 +16334,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -15697,7 +16351,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -15714,7 +16368,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -15731,7 +16385,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -15748,7 +16402,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -15765,7 +16419,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -15782,7 +16436,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -15794,7 +16448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -15805,7 +16459,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -15813,7 +16467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -15821,7 +16475,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -15829,7 +16483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -15837,7 +16491,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -15845,7 +16499,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -15853,7 +16507,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
@@ -15861,7 +16515,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
@@ -15869,7 +16523,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
@@ -15877,7 +16531,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
@@ -15885,17 +16539,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -15913,19 +16567,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB69695D-4376-40F6-8843-39E9145FC039}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.875" style="3"/>
+    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -15942,7 +16596,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -15959,7 +16613,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -15976,7 +16630,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -15993,7 +16647,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -16010,7 +16664,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -16027,7 +16681,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -16044,7 +16698,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -16061,7 +16715,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -16078,7 +16732,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -16095,7 +16749,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -16112,7 +16766,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -16129,7 +16783,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -16141,7 +16795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -16153,7 +16807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -16164,7 +16818,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -16172,7 +16826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -16180,7 +16834,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -16188,7 +16842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -16196,7 +16850,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -16204,7 +16858,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -16212,7 +16866,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
@@ -16220,7 +16874,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
@@ -16228,7 +16882,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
@@ -16236,7 +16890,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
@@ -16244,17 +16898,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -16272,19 +16926,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81150DD8-0930-408D-BFC8-717F4FA0F2BD}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.875" style="3"/>
+    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -16301,7 +16955,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -16318,7 +16972,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -16330,7 +16984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -16342,7 +16996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -16354,7 +17008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -16366,7 +17020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -16378,7 +17032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -16389,7 +17043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -16401,7 +17055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -16413,7 +17067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -16425,7 +17079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -16437,7 +17091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -16449,7 +17103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -16461,7 +17115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -16472,7 +17126,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -16480,7 +17134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -16488,7 +17142,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -16496,7 +17150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -16504,7 +17158,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -16512,7 +17166,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -16520,41 +17174,41 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -16572,19 +17226,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E7A6CB-75D8-40BA-8100-9864AFDBBD94}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.875" style="3"/>
+    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -16601,7 +17255,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -16618,7 +17272,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -16635,7 +17289,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -16652,7 +17306,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -16669,7 +17323,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -16686,7 +17340,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -16703,7 +17357,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -16714,7 +17368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -16726,7 +17380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -16738,7 +17392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -16750,7 +17404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -16762,7 +17416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -16774,7 +17428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -16786,7 +17440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -16797,7 +17451,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -16805,7 +17459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -16813,7 +17467,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -16821,7 +17475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -16829,7 +17483,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -16837,7 +17491,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -16845,7 +17499,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
@@ -16853,7 +17507,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
@@ -16861,7 +17515,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
@@ -16869,7 +17523,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
@@ -16877,17 +17531,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -16905,18 +17559,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452AA679-D54D-BB45-A949-CBDCD69908D4}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.875" style="3"/>
+    <col min="2" max="3" width="10.83203125" style="3"/>
     <col min="4" max="4" width="17.5" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -16933,7 +17587,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -16951,7 +17605,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -16969,7 +17623,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -16987,7 +17641,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -17005,7 +17659,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -17023,7 +17677,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -17035,7 +17689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -17047,7 +17701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -17059,7 +17713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -17071,7 +17725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -17083,7 +17737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -17095,7 +17749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -17107,7 +17761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -17119,7 +17773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -17130,7 +17784,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -17138,7 +17792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -17146,7 +17800,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -17154,7 +17808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -17162,7 +17816,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -17170,7 +17824,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -17178,43 +17832,43 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B22" s="10"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
       <c r="B23" s="10"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
       <c r="B24" s="10"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
       <c r="B25" s="10"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
       <c r="B26" s="10"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
       <c r="B27" s="10"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -17232,19 +17886,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B674D435-D420-471A-A5F5-9FBCD730FC8D}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>184</v>
       </c>
@@ -17261,7 +17915,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
@@ -17278,7 +17932,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
@@ -17290,7 +17944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -17302,7 +17956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>189</v>
       </c>
@@ -17314,7 +17968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -17326,7 +17980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>191</v>
       </c>
@@ -17337,7 +17991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>192</v>
       </c>
@@ -17348,7 +18002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>193</v>
       </c>
@@ -17360,7 +18014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
@@ -17372,7 +18026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>195</v>
       </c>
@@ -17384,7 +18038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>197</v>
       </c>
@@ -17396,7 +18050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>198</v>
       </c>
@@ -17408,7 +18062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>199</v>
       </c>
@@ -17420,7 +18074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C15" s="14" t="s">
         <v>200</v>
       </c>
@@ -17431,7 +18085,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>203</v>
       </c>
@@ -17439,7 +18093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>204</v>
       </c>
@@ -17447,7 +18101,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>206</v>
       </c>
@@ -17455,7 +18109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>207</v>
       </c>
@@ -17463,7 +18117,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>209</v>
       </c>
@@ -17471,7 +18125,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -17479,37 +18133,37 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>217</v>
       </c>
@@ -17520,300 +18174,6 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17 B19" xr:uid="{83018CC3-D5E2-45C3-8C9F-657C9C7AB673}">
-      <formula1>"Yes, No"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8307E2-C15E-3246-97E6-1FE53EC08157}">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
-  <cols>
-    <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.875" style="3"/>
-    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.875" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="6">
-        <v>45936</v>
-      </c>
-      <c r="C1" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D1" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B2" s="6">
-        <v>46118</v>
-      </c>
-      <c r="C2" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="C15" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B16" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B20" s="11">
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="11">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B28" s="3">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17 B19" xr:uid="{3D6AA655-0937-D041-BAA2-9AD8C4D94C09}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17830,6 +18190,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -18012,23 +18381,39 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+    <ds:schemaRef ds:uri="b0d30a24-05e2-4154-8fed-e579ddd987b0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377D626C-D8CE-D34C-AF93-A393D658E996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8854C7B6-F4DA-764D-ACDF-C7C149E0B9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17240" activeTab="2" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
@@ -16120,9 +16120,7 @@
       <c r="A18" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B18" s="24">
-        <v>10</v>
-      </c>
+      <c r="B18" s="24"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -18182,23 +18180,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -18381,25 +18362,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18416,4 +18396,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/training/upload/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C84D3BE5-BC42-8E41-A9A7-836767A3FDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{C84D3BE5-BC42-8E41-A9A7-836767A3FDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8B96FBC-4A2D-4534-AA47-2D4D849FC496}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17240" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
+    <workbookView xWindow="31470" yWindow="720" windowWidth="22995" windowHeight="13260" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
   <sheets>
     <sheet name="Class_Enrollment" sheetId="1" r:id="rId1"/>
@@ -1016,9 +1016,6 @@
   </cellStyles>
   <dxfs count="31">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1060,7 +1057,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1250,6 +1247,9 @@
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1307,27 +1307,27 @@
     <tableColumn id="17" xr3:uid="{69F27805-9427-9040-9579-C494AC53CBEC}" name="MGMT" dataDxfId="26"/>
     <tableColumn id="18" xr3:uid="{233B4BF2-C595-4046-9A7E-E57179A0E88E}" name="DUAL" dataDxfId="25"/>
     <tableColumn id="9" xr3:uid="{C08F3237-2D33-4620-A8D4-A1158062A4F4}" name="Educator AT" dataDxfId="24"/>
-    <tableColumn id="26" xr3:uid="{E174CA4A-F3BD-4F4A-96CA-8CC1FA3116B1}" name="FY26 Audiology Testing" dataDxfId="0"/>
-    <tableColumn id="25" xr3:uid="{F2A54F4F-FE80-44A6-A889-89F837B71978}" name="TDAC" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{233EB283-16C6-447C-907E-A1BDB618D235}" name="Neo SIM" dataDxfId="22"/>
-    <tableColumn id="15" xr3:uid="{ED293A2A-9DB9-480B-AE7E-823C99F10800}" name="Airway SIM" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{59549133-C9AB-476E-9F82-FC30D432A6B0}" name="Airway Decision SIM" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{7AC038BF-24B8-4FB6-BFAB-EBB4114C16B5}" name="Micro SIM" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{E1A8D9A8-36F0-F146-BD9C-FA31711EBC85}" name="FCCS" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{99A3E3DB-8870-4AA5-A3B8-C9C4E099D5FD}" name="PFCCS" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{FF0DAB42-3BB1-EA41-9413-27FD06C23ADF}" name="CRM" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{59CFB218-8779-064E-9C81-82BE200916B8}" name="STABLE" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{6F24D9FA-A378-4BD8-B0C3-67AF7CEC408F}" name="OB Lite" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{5A52CB73-6879-224E-B82B-E4888397F67A}" name="OB SIM" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{37E3A6D6-FD66-4356-84DD-0C85B02272C3}" name="ATLS" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{8F885C3C-6551-A341-A1E1-E87A8B120364}" name="Wed SM Q1" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{8FA5B1C0-F85D-9844-8174-379990B70432}" name="Thurs SM Q1" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{359CEC76-42FC-450D-8FC2-9533737922ED}" name="Wed SM Q2" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{FDDEC13D-F4E0-483E-BCAF-F167CDC1A8B2}" name="Thurs SM Q2" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{0365F14D-278F-4E55-9FED-06FBF05672B8}" name="Wed SM Q3" dataDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{02A3C20C-7212-4485-9509-92449910BCA0}" name="Thurs SM Q3" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{D363111F-4404-4357-8457-8A8A750BD852}" name="Wed SM Q4" dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{B3980D09-AB72-4B06-9605-2F8DC62FEF27}" name="Thurs SM Q4" dataDxfId="4"/>
+    <tableColumn id="26" xr3:uid="{E174CA4A-F3BD-4F4A-96CA-8CC1FA3116B1}" name="FY26 Audiology Testing" dataDxfId="23"/>
+    <tableColumn id="25" xr3:uid="{F2A54F4F-FE80-44A6-A889-89F837B71978}" name="TDAC" dataDxfId="22"/>
+    <tableColumn id="16" xr3:uid="{233EB283-16C6-447C-907E-A1BDB618D235}" name="Neo SIM" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{ED293A2A-9DB9-480B-AE7E-823C99F10800}" name="Airway SIM" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{59549133-C9AB-476E-9F82-FC30D432A6B0}" name="Airway Decision SIM" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{7AC038BF-24B8-4FB6-BFAB-EBB4114C16B5}" name="Micro SIM" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{E1A8D9A8-36F0-F146-BD9C-FA31711EBC85}" name="FCCS" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{99A3E3DB-8870-4AA5-A3B8-C9C4E099D5FD}" name="PFCCS" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{FF0DAB42-3BB1-EA41-9413-27FD06C23ADF}" name="CRM" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{59CFB218-8779-064E-9C81-82BE200916B8}" name="STABLE" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{6F24D9FA-A378-4BD8-B0C3-67AF7CEC408F}" name="OB Lite" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{5A52CB73-6879-224E-B82B-E4888397F67A}" name="OB SIM" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{37E3A6D6-FD66-4356-84DD-0C85B02272C3}" name="ATLS" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{8F885C3C-6551-A341-A1E1-E87A8B120364}" name="Wed SM Q1" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{8FA5B1C0-F85D-9844-8174-379990B70432}" name="Thurs SM Q1" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{359CEC76-42FC-450D-8FC2-9533737922ED}" name="Wed SM Q2" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{FDDEC13D-F4E0-483E-BCAF-F167CDC1A8B2}" name="Thurs SM Q2" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{0365F14D-278F-4E55-9FED-06FBF05672B8}" name="Wed SM Q3" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{02A3C20C-7212-4485-9509-92449910BCA0}" name="Thurs SM Q3" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{D363111F-4404-4357-8457-8A8A750BD852}" name="Wed SM Q4" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{B3980D09-AB72-4B06-9605-2F8DC62FEF27}" name="Thurs SM Q4" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1343,9 +1343,9 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2672EBD8-969E-42D0-823E-342D8F577BC7}" name="Course" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{C65C019C-A891-46EF-BA31-BD8C3BF273AC}" name="Date" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{C97A581D-59F3-49CE-ABF9-B11A243044E6}" name="Column1" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{2672EBD8-969E-42D0-823E-342D8F577BC7}" name="Course" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{C65C019C-A891-46EF-BA31-BD8C3BF273AC}" name="Date" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{C97A581D-59F3-49CE-ABF9-B11A243044E6}" name="Column1" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{D7761227-C451-4885-931A-57652CE4D3AD}" name="Column2"/>
     <tableColumn id="5" xr3:uid="{17C507F1-1F99-439B-9B4A-F383DF7525D7}" name="Column3"/>
     <tableColumn id="6" xr3:uid="{614E0677-FB05-438C-B25C-C8A51FAB1181}" name="Column4"/>
@@ -1673,30 +1673,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE3E758-B252-634C-B9B3-AE34AE7DE6C7}">
   <dimension ref="A1:Z145"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" style="1" customWidth="1"/>
-    <col min="5" max="7" width="16.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="16.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="21.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="1" customWidth="1"/>
     <col min="14" max="14" width="9.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.6640625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.1640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.6640625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="15.1640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.1640625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="10.83203125" style="1"/>
+    <col min="15" max="15" width="12.125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="15.125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.125" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>46</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>47</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>48</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>51</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>52</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>53</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>54</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>55</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>56</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>57</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>58</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>59</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>60</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>61</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>62</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>63</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>64</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>65</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>66</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>67</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>69</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>70</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>71</v>
       </c>
@@ -5262,7 +5262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>72</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>73</v>
       </c>
@@ -5416,7 +5416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>74</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>75</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>76</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>77</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>78</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>79</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>80</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>81</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>82</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>83</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>84</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>85</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>86</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>87</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>88</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>89</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>90</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>91</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>92</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>93</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>94</v>
       </c>
@@ -7054,7 +7054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>95</v>
       </c>
@@ -7131,7 +7131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>96</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>97</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>98</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>99</v>
       </c>
@@ -7442,7 +7442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>100</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>101</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>102</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>103</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>104</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>105</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>106</v>
       </c>
@@ -7978,7 +7978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>107</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>109</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>110</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>111</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>112</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>113</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>114</v>
       </c>
@@ -8181,7 +8181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>115</v>
       </c>
@@ -8210,7 +8210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>116</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>117</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>118</v>
       </c>
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>119</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>120</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>121</v>
       </c>
@@ -8384,7 +8384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>122</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>123</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>124</v>
       </c>
@@ -8477,7 +8477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>126</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>127</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>128</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>129</v>
       </c>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>130</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>131</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>132</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>133</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>134</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>135</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>136</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>137</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>138</v>
       </c>
@@ -8941,7 +8941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>139</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>140</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>141</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>143</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>144</v>
       </c>
       <c r="F115" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N115" s="2" t="b">
         <v>1</v>
@@ -9078,7 +9078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>145</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>144</v>
       </c>
       <c r="F116" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N116" s="2" t="b">
         <v>1</v>
@@ -9110,7 +9110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>146</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>144</v>
       </c>
       <c r="F117" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N117" s="2" t="b">
         <v>1</v>
@@ -9142,7 +9142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>147</v>
       </c>
@@ -9150,7 +9150,7 @@
         <v>144</v>
       </c>
       <c r="F118" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N118" s="2" t="b">
         <v>1</v>
@@ -9174,7 +9174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>148</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>144</v>
       </c>
       <c r="F119" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" s="2" t="b">
         <v>1</v>
@@ -9206,7 +9206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>149</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>144</v>
       </c>
       <c r="F120" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" s="2" t="b">
         <v>1</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>150</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>144</v>
       </c>
       <c r="F121" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" s="2" t="b">
         <v>1</v>
@@ -9270,7 +9270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>151</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>144</v>
       </c>
       <c r="F122" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" s="2" t="b">
         <v>1</v>
@@ -9302,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:26" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>152</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>144</v>
       </c>
       <c r="F123" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N123" s="2" t="b">
         <v>1</v>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>153</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>144</v>
       </c>
       <c r="F124" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124" s="2" t="b">
         <v>1</v>
@@ -9366,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>154</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>144</v>
       </c>
       <c r="F125" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N125" s="2" t="b">
         <v>1</v>
@@ -9398,7 +9398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>155</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>144</v>
       </c>
       <c r="F126" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N126" s="2" t="b">
         <v>1</v>
@@ -9430,7 +9430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>156</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>144</v>
       </c>
       <c r="F127" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N127" s="2" t="b">
         <v>1</v>
@@ -9462,7 +9462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>157</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>144</v>
       </c>
       <c r="F128" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N128" s="2" t="b">
         <v>1</v>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>158</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>144</v>
       </c>
       <c r="F129" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129" s="2" t="b">
         <v>1</v>
@@ -9526,7 +9526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>159</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>144</v>
       </c>
       <c r="F130" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N130" s="2" t="b">
         <v>1</v>
@@ -9558,7 +9558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>160</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>144</v>
       </c>
       <c r="F131" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131" s="2" t="b">
         <v>1</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>161</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>144</v>
       </c>
       <c r="F132" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N132" s="2" t="b">
         <v>1</v>
@@ -9622,7 +9622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>162</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>144</v>
       </c>
       <c r="F133" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N133" s="2" t="b">
         <v>1</v>
@@ -9654,7 +9654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>163</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>165</v>
       </c>
@@ -9718,7 +9718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>166</v>
       </c>
@@ -9750,7 +9750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>167</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>168</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>169</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>170</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>171</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>172</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>173</v>
       </c>
@@ -9974,7 +9974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>174</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>175</v>
       </c>
@@ -10049,15 +10049,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8307E2-C15E-3246-97E6-1FE53EC08157}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="2" max="3" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -10127,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -10139,7 +10139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -10150,7 +10150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -10173,7 +10173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -10185,7 +10185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -10221,7 +10221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -10260,7 +10260,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -10268,7 +10268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -10292,37 +10292,37 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -10343,15 +10343,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58626D5E-CF7D-7040-8A8E-EE19354196C8}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="2" max="3" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -10365,7 +10365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -10404,7 +10404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -10426,7 +10426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -10496,7 +10496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -10520,7 +10520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -10555,7 +10555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -10563,7 +10563,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -10579,37 +10579,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -10630,15 +10630,15 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9BC729-92D2-4067-85BC-DFDCD994C98C}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="2" max="3" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -10771,7 +10771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -10807,7 +10807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -10834,7 +10834,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -10850,7 +10850,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -10866,37 +10866,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -10917,15 +10917,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D88D2FE4-23CC-491D-BD62-D960817AB0D2}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -10939,7 +10939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -10978,7 +10978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -11011,7 +11011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -11070,7 +11070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -11121,7 +11121,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -11129,7 +11129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -11153,37 +11153,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -11204,16 +11204,16 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24407AE7-238F-42BD-B8EA-6F88E165DF83}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -11255,7 +11255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -11266,7 +11266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -11299,7 +11299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -11346,7 +11346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -11358,7 +11358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -11370,7 +11370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -11393,7 +11393,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -11401,7 +11401,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -11409,7 +11409,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -11417,7 +11417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -11441,37 +11441,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -11492,15 +11492,15 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7578FEE-5B85-43AD-81EE-212BA4C5295B}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -11553,7 +11553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -11564,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -11575,7 +11575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -11586,7 +11586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -11597,7 +11597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -11621,7 +11621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -11645,7 +11645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -11657,7 +11657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -11669,7 +11669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -11696,7 +11696,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -11712,7 +11712,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -11728,37 +11728,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -11779,16 +11779,16 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CEAB94E-7986-48ED-9C86-1B1BBA3C1E49}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -11830,7 +11830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -11841,7 +11841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -11863,7 +11863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -11874,7 +11874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -11897,7 +11897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -11921,7 +11921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -11945,7 +11945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -11968,7 +11968,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -12000,7 +12000,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -12016,37 +12016,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -12067,15 +12067,15 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC058F5-09C7-4162-863E-422D32EBC74A}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -12150,7 +12150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -12161,7 +12161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -12172,7 +12172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -12196,7 +12196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -12244,7 +12244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -12279,7 +12279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -12287,7 +12287,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -12295,7 +12295,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -12303,37 +12303,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -12354,16 +12354,16 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFE2395-82E7-4A11-91BF-FB62274BB4C3}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -12377,7 +12377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -12391,7 +12391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -12405,7 +12405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -12416,7 +12416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -12427,7 +12427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -12449,7 +12449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -12543,7 +12543,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -12551,7 +12551,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -12559,7 +12559,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -12567,7 +12567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -12575,7 +12575,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -12583,7 +12583,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -12591,37 +12591,37 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -12642,15 +12642,15 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{251C4556-B6F5-4EAB-AE0D-DC7FA135F386}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="2" max="3" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -12667,7 +12667,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -12701,7 +12701,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -12752,7 +12752,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -12786,7 +12786,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -12810,7 +12810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -12822,7 +12822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -12834,7 +12834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -12869,7 +12869,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -12885,7 +12885,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -12901,7 +12901,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -12917,37 +12917,37 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -12968,16 +12968,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD174F3-4421-40E9-ADA5-4D51B58F838B}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -12994,7 +12994,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -13045,7 +13045,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -13062,7 +13062,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -13079,7 +13079,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -13096,7 +13096,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -13130,7 +13130,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -13147,7 +13147,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -13164,7 +13164,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -13181,7 +13181,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -13210,7 +13210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -13221,7 +13221,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -13229,7 +13229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -13253,7 +13253,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
@@ -13285,7 +13285,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
@@ -13293,7 +13293,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
@@ -13301,17 +13301,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -13332,16 +13332,16 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73369AC4-C9B4-42DD-BF9C-2665EDC8C92A}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -13375,7 +13375,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -13399,7 +13399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -13411,7 +13411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -13423,7 +13423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -13470,7 +13470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -13494,7 +13494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -13506,7 +13506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -13518,7 +13518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -13529,7 +13529,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -13545,7 +13545,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -13561,7 +13561,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -13577,41 +13577,41 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -13632,15 +13632,15 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DEE273-7DC8-284A-9883-269CFB150B79}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="2" max="3" width="10.875" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -13657,7 +13657,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -13674,7 +13674,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -13691,7 +13691,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -13708,7 +13708,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -13725,7 +13725,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -13759,7 +13759,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -13782,7 +13782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -13853,7 +13853,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -13861,7 +13861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
@@ -13917,7 +13917,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
@@ -13925,7 +13925,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
@@ -13933,17 +13933,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -13964,17 +13964,17 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0587D0-89DF-4D05-A902-12BFC82DD3EC}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -13991,7 +13991,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -14008,7 +14008,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -14025,7 +14025,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -14059,7 +14059,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -14076,7 +14076,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -14093,7 +14093,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -14110,7 +14110,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -14178,7 +14178,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -14195,7 +14195,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -14212,7 +14212,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -14231,7 +14231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -14239,7 +14239,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -14247,7 +14247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -14255,7 +14255,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -14271,41 +14271,41 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -14326,13 +14326,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D7DB1A-8C06-5D43-8D41-553EA9E8A37B}">
   <dimension ref="A1:N99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>216</v>
       </c>
@@ -14376,7 +14376,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>223</v>
       </c>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="J2" s="16"/>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>228</v>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="J3" s="16"/>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="E4" s="6">
         <v>46063</v>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="J4" s="16"/>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="E5" s="6">
         <v>46091</v>
@@ -14462,7 +14462,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="E6" s="6">
         <v>46114</v>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="E7" s="6">
         <v>46170</v>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="F8" s="8">
         <v>46294</v>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="J8" s="16"/>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H9" s="16" t="s">
         <v>227</v>
       </c>
@@ -14518,7 +14518,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H10" s="16" t="s">
         <v>227</v>
       </c>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H11" s="16" t="s">
         <v>227</v>
       </c>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="H12" s="16" t="s">
         <v>227</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="H13" s="16" t="s">
         <v>227</v>
@@ -14558,7 +14558,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="H14" s="16" t="s">
         <v>231</v>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="J14" s="16"/>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="H15" s="16" t="s">
         <v>231</v>
@@ -14580,7 +14580,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="H16" s="16" t="s">
         <v>231</v>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H17" s="16" t="s">
         <v>231</v>
       </c>
@@ -14599,7 +14599,7 @@
       </c>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H18" s="16" t="s">
         <v>231</v>
       </c>
@@ -14608,7 +14608,7 @@
       </c>
       <c r="J18" s="16"/>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H19" s="16" t="s">
         <v>231</v>
       </c>
@@ -14619,7 +14619,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="H20" s="16" t="s">
         <v>231</v>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="J20" s="16"/>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="H21" s="16" t="s">
         <v>231</v>
@@ -14639,7 +14639,7 @@
       </c>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="H22" s="16" t="s">
         <v>231</v>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="J22" s="16"/>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="H23" s="16" t="s">
         <v>231</v>
@@ -14661,7 +14661,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="H24" s="16" t="s">
         <v>231</v>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="J24" s="16"/>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H25" s="16" t="s">
         <v>231</v>
       </c>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H26" s="16" t="s">
         <v>232</v>
       </c>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="J26" s="16"/>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="H27" s="16" t="s">
         <v>232</v>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="J27" s="16"/>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="H28" s="16" t="s">
         <v>232</v>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="J28" s="16"/>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="H29" s="16" t="s">
         <v>232</v>
@@ -14719,7 +14719,7 @@
       </c>
       <c r="J29" s="16"/>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="H30" s="16" t="s">
         <v>232</v>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="J30" s="16"/>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="H31" s="16" t="s">
         <v>232</v>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="J31" s="16"/>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="H32" s="16" t="s">
         <v>232</v>
@@ -14749,7 +14749,7 @@
       </c>
       <c r="J32" s="16"/>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H33" s="16" t="s">
         <v>233</v>
       </c>
@@ -14758,7 +14758,7 @@
       </c>
       <c r="J33" s="16"/>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H34" s="16" t="s">
         <v>233</v>
       </c>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="J34" s="16"/>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H35" s="16" t="s">
         <v>233</v>
       </c>
@@ -14776,7 +14776,7 @@
       </c>
       <c r="J35" s="16"/>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H36" s="16" t="s">
         <v>233</v>
       </c>
@@ -14785,7 +14785,7 @@
       </c>
       <c r="J36" s="16"/>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H37" s="16" t="s">
         <v>233</v>
       </c>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="J37" s="16"/>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H38" s="16" t="s">
         <v>233</v>
       </c>
@@ -14803,7 +14803,7 @@
       </c>
       <c r="J38" s="16"/>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H39" s="16" t="s">
         <v>233</v>
       </c>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="J39" s="16"/>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="H40" s="16" t="s">
         <v>233</v>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="J40" s="16"/>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>15</v>
       </c>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="J41" s="16"/>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>46253</v>
       </c>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="J42" s="16"/>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>46260</v>
       </c>
@@ -14860,7 +14860,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>46266</v>
       </c>
@@ -14874,7 +14874,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>46274</v>
       </c>
@@ -14888,7 +14888,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>46280</v>
       </c>
@@ -14900,7 +14900,7 @@
       </c>
       <c r="J46" s="16"/>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>46288</v>
       </c>
@@ -14912,7 +14912,7 @@
       </c>
       <c r="J47" s="16"/>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>46294</v>
       </c>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="J48" s="16"/>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>16</v>
       </c>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="J49" s="16"/>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>226</v>
       </c>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="J50" s="16"/>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="H51" s="16" t="s">
         <v>235</v>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="J51" s="16"/>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="H52" s="16" t="s">
         <v>235</v>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="J52" s="16"/>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="H53" s="16" t="s">
         <v>235</v>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="J53" s="16"/>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="H54" s="16" t="s">
         <v>235</v>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="J54" s="16"/>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="H55" s="16" t="s">
         <v>235</v>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="J55" s="16"/>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="H56" s="16" t="s">
         <v>235</v>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="J56" s="16"/>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H57" s="16" t="s">
         <v>235</v>
       </c>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="J57" s="16"/>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H58" s="16" t="s">
         <v>236</v>
       </c>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="J58" s="16"/>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H59" s="16" t="s">
         <v>236</v>
       </c>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="J59" s="16"/>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H60" s="16" t="s">
         <v>236</v>
       </c>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="J60" s="16"/>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H61" s="16" t="s">
         <v>236</v>
       </c>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="J61" s="16"/>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H62" s="16" t="s">
         <v>236</v>
       </c>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="J62" s="16"/>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H63" s="16" t="s">
         <v>236</v>
       </c>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="J63" s="16"/>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H64" s="16" t="s">
         <v>236</v>
       </c>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="J64" s="16"/>
     </row>
-    <row r="65" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H65" s="16" t="s">
         <v>236</v>
       </c>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="J65" s="16"/>
     </row>
-    <row r="66" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H66" s="16" t="s">
         <v>236</v>
       </c>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="J66" s="16"/>
     </row>
-    <row r="67" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H67" s="16" t="s">
         <v>236</v>
       </c>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="J67" s="16"/>
     </row>
-    <row r="68" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H68" s="16" t="s">
         <v>236</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="69" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H69" s="16" t="s">
         <v>236</v>
       </c>
@@ -15129,7 +15129,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="70" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H70" s="16" t="s">
         <v>236</v>
       </c>
@@ -15140,7 +15140,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="71" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H71" s="16" t="s">
         <v>238</v>
       </c>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="J71" s="16"/>
     </row>
-    <row r="72" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H72" s="16" t="s">
         <v>238</v>
       </c>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="J72" s="16"/>
     </row>
-    <row r="73" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H73" s="16" t="s">
         <v>238</v>
       </c>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="J73" s="16"/>
     </row>
-    <row r="74" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H74" s="16" t="s">
         <v>238</v>
       </c>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="J74" s="16"/>
     </row>
-    <row r="75" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H75" s="16" t="s">
         <v>238</v>
       </c>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="J75" s="16"/>
     </row>
-    <row r="76" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H76" s="16" t="s">
         <v>238</v>
       </c>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="J76" s="16"/>
     </row>
-    <row r="77" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H77" s="16" t="s">
         <v>238</v>
       </c>
@@ -15203,7 +15203,7 @@
       </c>
       <c r="J77" s="16"/>
     </row>
-    <row r="78" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H78" s="16" t="s">
         <v>239</v>
       </c>
@@ -15220,7 +15220,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="16"/>
     </row>
-    <row r="79" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H79" s="16" t="s">
         <v>240</v>
       </c>
@@ -15237,7 +15237,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="16"/>
     </row>
-    <row r="80" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H80" s="16" t="s">
         <v>241</v>
       </c>
@@ -15254,7 +15254,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="16"/>
     </row>
-    <row r="81" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H81" s="16" t="s">
         <v>242</v>
       </c>
@@ -15265,7 +15265,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="16"/>
     </row>
-    <row r="82" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H82" s="16" t="s">
         <v>10</v>
       </c>
@@ -15278,7 +15278,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="16"/>
     </row>
-    <row r="83" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H83" s="16" t="s">
         <v>10</v>
       </c>
@@ -15291,7 +15291,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="16"/>
     </row>
-    <row r="84" spans="8:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="8:14" x14ac:dyDescent="0.25">
       <c r="H84" s="16" t="s">
         <v>11</v>
       </c>
@@ -15304,7 +15304,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="16"/>
     </row>
-    <row r="85" spans="8:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="8:14" x14ac:dyDescent="0.25">
       <c r="H85" s="16" t="s">
         <v>11</v>
       </c>
@@ -15317,7 +15317,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="16"/>
     </row>
-    <row r="86" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H86" s="16" t="s">
         <v>247</v>
       </c>
@@ -15330,7 +15330,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="16"/>
     </row>
-    <row r="87" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H87" s="16" t="s">
         <v>247</v>
       </c>
@@ -15343,7 +15343,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="16"/>
     </row>
-    <row r="88" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H88" s="16" t="s">
         <v>13</v>
       </c>
@@ -15356,7 +15356,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="16"/>
     </row>
-    <row r="89" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H89" s="16" t="s">
         <v>13</v>
       </c>
@@ -15369,7 +15369,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="16"/>
     </row>
-    <row r="90" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H90" s="16" t="s">
         <v>13</v>
       </c>
@@ -15382,7 +15382,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="16"/>
     </row>
-    <row r="91" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H91" s="16" t="s">
         <v>13</v>
       </c>
@@ -15395,7 +15395,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="16"/>
     </row>
-    <row r="92" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H92" s="16" t="s">
         <v>13</v>
       </c>
@@ -15408,7 +15408,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="16"/>
     </row>
-    <row r="93" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H93" s="16" t="s">
         <v>13</v>
       </c>
@@ -15421,7 +15421,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="16"/>
     </row>
-    <row r="94" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H94" s="16" t="s">
         <v>248</v>
       </c>
@@ -15444,7 +15444,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H95" s="16" t="s">
         <v>250</v>
       </c>
@@ -15467,7 +15467,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="96" spans="8:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="8:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="H96" s="16" t="s">
         <v>251</v>
       </c>
@@ -15490,7 +15490,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="8:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="8:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H97" s="16" t="s">
         <v>253</v>
       </c>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="J97" s="16"/>
     </row>
-    <row r="98" spans="8:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="8:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H98" s="16" t="s">
         <v>254</v>
       </c>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="J98" s="16"/>
     </row>
-    <row r="99" spans="8:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="8:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="H99" s="16" t="s">
         <v>255</v>
       </c>
@@ -15528,13 +15528,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE5E83A-B444-4206-8DA8-1368EF05AF5C}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="13">
         <v>45957</v>
       </c>
@@ -15559,7 +15559,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>124</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -15605,7 +15605,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -15628,7 +15628,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>129</v>
       </c>
@@ -15674,7 +15674,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>259</v>
       </c>
@@ -15720,7 +15720,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>131</v>
       </c>
@@ -15743,7 +15743,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -15766,7 +15766,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -15789,7 +15789,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -15812,7 +15812,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -15835,7 +15835,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>137</v>
       </c>
@@ -15858,7 +15858,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>138</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>139</v>
       </c>
@@ -15904,7 +15904,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -15927,7 +15927,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>141</v>
       </c>
@@ -15950,7 +15950,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>142</v>
       </c>
@@ -15981,20 +15981,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09EEA88E-7AEE-574F-BC90-87FF2ABA87C3}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="15.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>176</v>
       </c>
@@ -16020,7 +16020,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>178</v>
       </c>
@@ -16046,7 +16046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>179</v>
       </c>
@@ -16063,7 +16063,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>180</v>
       </c>
@@ -16080,7 +16080,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>181</v>
       </c>
@@ -16097,7 +16097,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>182</v>
       </c>
@@ -16109,7 +16109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>183</v>
       </c>
@@ -16121,7 +16121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>184</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>185</v>
       </c>
@@ -16145,7 +16145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>186</v>
       </c>
@@ -16157,7 +16157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>187</v>
       </c>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>189</v>
       </c>
@@ -16181,7 +16181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>190</v>
       </c>
@@ -16193,7 +16193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>191</v>
       </c>
@@ -16205,7 +16205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C15" s="22" t="s">
         <v>192</v>
       </c>
@@ -16216,7 +16216,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>195</v>
       </c>
@@ -16224,7 +16224,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>196</v>
       </c>
@@ -16232,13 +16232,13 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>198</v>
       </c>
       <c r="B18" s="24"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>199</v>
       </c>
@@ -16246,7 +16246,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>201</v>
       </c>
@@ -16254,7 +16254,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>202</v>
       </c>
@@ -16262,41 +16262,41 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>203</v>
       </c>
       <c r="B22" s="25"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>204</v>
       </c>
       <c r="B23" s="25"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>205</v>
       </c>
       <c r="B24" s="25"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B25" s="25"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>209</v>
       </c>
@@ -16314,16 +16314,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D169A3-4EB4-4BAF-ABF2-90D52870D9B1}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -16343,7 +16343,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -16363,7 +16363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -16380,7 +16380,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -16397,7 +16397,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -16414,7 +16414,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -16448,7 +16448,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -16465,7 +16465,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -16482,7 +16482,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -16499,7 +16499,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -16516,7 +16516,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -16550,7 +16550,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -16562,7 +16562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -16573,7 +16573,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -16581,7 +16581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -16589,7 +16589,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -16597,7 +16597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -16613,7 +16613,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -16621,7 +16621,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
@@ -16629,7 +16629,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
@@ -16637,7 +16637,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
@@ -16645,7 +16645,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
@@ -16653,17 +16653,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -16684,16 +16684,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB69695D-4376-40F6-8843-39E9145FC039}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -16727,7 +16727,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -16744,7 +16744,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -16761,7 +16761,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -16778,7 +16778,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -16795,7 +16795,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -16812,7 +16812,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -16829,7 +16829,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -16846,7 +16846,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -16863,7 +16863,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -16880,7 +16880,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -16897,7 +16897,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -16909,7 +16909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -16921,7 +16921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -16932,7 +16932,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -16940,7 +16940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -16948,7 +16948,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -16956,7 +16956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -16964,7 +16964,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -16972,7 +16972,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
@@ -16988,7 +16988,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
@@ -16996,7 +16996,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
@@ -17012,17 +17012,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -17043,16 +17043,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81150DD8-0930-408D-BFC8-717F4FA0F2BD}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -17069,7 +17069,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -17086,7 +17086,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -17098,7 +17098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -17110,7 +17110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -17122,7 +17122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -17134,7 +17134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -17146,7 +17146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -17157,7 +17157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -17169,7 +17169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -17181,7 +17181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -17193,7 +17193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -17205,7 +17205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -17229,7 +17229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -17240,7 +17240,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -17248,7 +17248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -17256,7 +17256,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -17264,7 +17264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -17272,7 +17272,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -17280,7 +17280,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -17288,41 +17288,41 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
       <c r="B22" s="11"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B24" s="11"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -17343,16 +17343,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E7A6CB-75D8-40BA-8100-9864AFDBBD94}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="26.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -17369,7 +17369,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -17386,7 +17386,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -17403,7 +17403,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -17420,7 +17420,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -17437,7 +17437,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -17454,7 +17454,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -17471,7 +17471,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -17482,7 +17482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -17494,7 +17494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -17506,7 +17506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -17518,7 +17518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -17530,7 +17530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -17554,7 +17554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -17565,7 +17565,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -17573,7 +17573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -17597,7 +17597,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -17605,7 +17605,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -17613,7 +17613,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
@@ -17621,7 +17621,7 @@
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
@@ -17629,7 +17629,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
@@ -17637,7 +17637,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
@@ -17645,17 +17645,17 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -17676,15 +17676,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452AA679-D54D-BB45-A949-CBDCD69908D4}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="3"/>
+    <col min="2" max="3" width="10.875" style="3"/>
     <col min="4" max="4" width="17.5" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -17701,7 +17701,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -17719,7 +17719,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -17737,7 +17737,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -17755,7 +17755,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -17773,7 +17773,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -17791,7 +17791,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -17815,7 +17815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -17827,7 +17827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -17839,7 +17839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -17851,7 +17851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -17863,7 +17863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -17887,7 +17887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -17906,7 +17906,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -17914,7 +17914,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -17922,7 +17922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -17930,7 +17930,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -17946,43 +17946,43 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
       <c r="B22" s="10"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
       <c r="B23" s="10"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B24" s="10"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B25" s="10"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B26" s="10"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
       <c r="B27" s="10"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -18003,16 +18003,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B674D435-D420-471A-A5F5-9FBCD730FC8D}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3"/>
-    <col min="4" max="4" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="15.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>176</v>
       </c>
@@ -18029,7 +18029,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>178</v>
       </c>
@@ -18046,7 +18046,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -18058,7 +18058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -18070,7 +18070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>181</v>
       </c>
@@ -18082,7 +18082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>182</v>
       </c>
@@ -18094,7 +18094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>183</v>
       </c>
@@ -18105,7 +18105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>184</v>
       </c>
@@ -18116,7 +18116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>185</v>
       </c>
@@ -18128,7 +18128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>186</v>
       </c>
@@ -18140,7 +18140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>187</v>
       </c>
@@ -18152,7 +18152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>189</v>
       </c>
@@ -18164,7 +18164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
@@ -18176,7 +18176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>191</v>
       </c>
@@ -18188,7 +18188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>192</v>
       </c>
@@ -18199,7 +18199,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>195</v>
       </c>
@@ -18207,7 +18207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>196</v>
       </c>
@@ -18215,7 +18215,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>198</v>
       </c>
@@ -18223,7 +18223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>199</v>
       </c>
@@ -18231,7 +18231,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>201</v>
       </c>
@@ -18239,7 +18239,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>202</v>
       </c>
@@ -18247,37 +18247,37 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>209</v>
       </c>
@@ -18296,6 +18296,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -18478,24 +18495,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18512,22 +18530,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D586707C-E775-4E5A-99C2-309198B868E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B49C4EA-3204-479D-91E5-4149CC0A998E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31470" yWindow="720" windowWidth="22995" windowHeight="13260" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
+    <workbookView xWindow="31470" yWindow="720" windowWidth="22995" windowHeight="13260" activeTab="2" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
   <sheets>
     <sheet name="Class_Enrollment" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="268">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -704,6 +704,9 @@
   </si>
   <si>
     <t>SESSION_LENGTH</t>
+  </si>
+  <si>
+    <t>COUNT_EXEMPT</t>
   </si>
   <si>
     <t>BAW</t>
@@ -14228,7 +14231,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -14245,7 +14248,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -14262,7 +14265,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -14279,7 +14282,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -14296,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -14313,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -14330,7 +14333,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -14347,7 +14350,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -14364,7 +14367,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -14381,7 +14384,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -14398,7 +14401,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -14415,7 +14418,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -14432,7 +14435,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -14449,7 +14452,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -14574,7 +14577,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>11</v>
@@ -14595,36 +14598,36 @@
         <v>17</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:14" hidden="1">
       <c r="A2" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D2" s="6">
         <v>46042</v>
@@ -14636,10 +14639,10 @@
         <v>46253</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I2" s="18">
         <v>45931</v>
@@ -14649,10 +14652,10 @@
     <row r="3" spans="1:14" hidden="1">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E3" s="6">
         <v>46035</v>
@@ -14661,7 +14664,7 @@
         <v>46260</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I3" s="18">
         <v>45966</v>
@@ -14677,7 +14680,7 @@
         <v>46266</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I4" s="18">
         <v>45994</v>
@@ -14693,13 +14696,13 @@
         <v>46274</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I5" s="18">
         <v>46029</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:14" hidden="1">
@@ -14711,7 +14714,7 @@
         <v>46280</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I6" s="18">
         <v>46057</v>
@@ -14727,7 +14730,7 @@
         <v>46288</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I7" s="18">
         <v>46085</v>
@@ -14740,7 +14743,7 @@
         <v>46294</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I8" s="18">
         <v>46113</v>
@@ -14749,18 +14752,18 @@
     </row>
     <row r="9" spans="1:14" hidden="1">
       <c r="H9" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I9" s="18">
         <v>46148</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:14" hidden="1">
       <c r="H10" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I10" s="18">
         <v>46176</v>
@@ -14769,7 +14772,7 @@
     </row>
     <row r="11" spans="1:14" hidden="1">
       <c r="H11" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I11" s="18">
         <v>46204</v>
@@ -14779,7 +14782,7 @@
     <row r="12" spans="1:14" hidden="1">
       <c r="A12" s="5"/>
       <c r="H12" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I12" s="18">
         <v>46239</v>
@@ -14789,19 +14792,19 @@
     <row r="13" spans="1:14" hidden="1">
       <c r="A13" s="5"/>
       <c r="H13" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I13" s="18">
         <v>46267</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:14" hidden="1">
       <c r="A14" s="5"/>
       <c r="H14" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I14" s="18">
         <v>45946</v>
@@ -14811,19 +14814,19 @@
     <row r="15" spans="1:14" hidden="1">
       <c r="A15" s="5"/>
       <c r="H15" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I15" s="18">
         <v>45981</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:14" hidden="1">
       <c r="A16" s="5"/>
       <c r="H16" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I16" s="18">
         <v>46009</v>
@@ -14832,7 +14835,7 @@
     </row>
     <row r="17" spans="1:10" hidden="1">
       <c r="H17" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I17" s="18">
         <v>46037</v>
@@ -14841,7 +14844,7 @@
     </row>
     <row r="18" spans="1:10" hidden="1">
       <c r="H18" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I18" s="18">
         <v>46072</v>
@@ -14850,19 +14853,19 @@
     </row>
     <row r="19" spans="1:10" hidden="1">
       <c r="H19" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I19" s="18">
         <v>46100</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:10" hidden="1">
       <c r="A20" s="5"/>
       <c r="H20" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I20" s="18">
         <v>46128</v>
@@ -14872,7 +14875,7 @@
     <row r="21" spans="1:10" hidden="1">
       <c r="A21" s="5"/>
       <c r="H21" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I21" s="18">
         <v>46163</v>
@@ -14882,7 +14885,7 @@
     <row r="22" spans="1:10" hidden="1">
       <c r="A22" s="5"/>
       <c r="H22" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I22" s="18">
         <v>46191</v>
@@ -14892,19 +14895,19 @@
     <row r="23" spans="1:10" hidden="1">
       <c r="A23" s="5"/>
       <c r="H23" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I23" s="18">
         <v>46219</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="1:10" hidden="1">
       <c r="A24" s="5"/>
       <c r="H24" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I24" s="18">
         <v>46254</v>
@@ -14913,7 +14916,7 @@
     </row>
     <row r="25" spans="1:10" hidden="1">
       <c r="H25" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I25" s="18">
         <v>46282</v>
@@ -14922,7 +14925,7 @@
     </row>
     <row r="26" spans="1:10" hidden="1">
       <c r="H26" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I26" s="18">
         <v>45945</v>
@@ -14932,7 +14935,7 @@
     <row r="27" spans="1:10" hidden="1">
       <c r="A27" s="5"/>
       <c r="H27" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I27" s="18">
         <v>45959</v>
@@ -14942,7 +14945,7 @@
     <row r="28" spans="1:10" hidden="1">
       <c r="A28" s="5"/>
       <c r="H28" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I28" s="18">
         <v>45979</v>
@@ -14952,7 +14955,7 @@
     <row r="29" spans="1:10" hidden="1">
       <c r="A29" s="5"/>
       <c r="H29" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I29" s="18">
         <v>46001</v>
@@ -14962,7 +14965,7 @@
     <row r="30" spans="1:10" hidden="1">
       <c r="A30" s="5"/>
       <c r="H30" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I30" s="18">
         <v>46008</v>
@@ -14972,7 +14975,7 @@
     <row r="31" spans="1:10" hidden="1">
       <c r="A31" s="5"/>
       <c r="H31" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I31" s="18">
         <v>46028</v>
@@ -14982,7 +14985,7 @@
     <row r="32" spans="1:10" hidden="1">
       <c r="A32" s="5"/>
       <c r="H32" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I32" s="18">
         <v>46043</v>
@@ -14991,7 +14994,7 @@
     </row>
     <row r="33" spans="1:10" hidden="1">
       <c r="H33" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I33" s="18">
         <v>46050</v>
@@ -15000,7 +15003,7 @@
     </row>
     <row r="34" spans="1:10" hidden="1">
       <c r="H34" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I34" s="18">
         <v>46056</v>
@@ -15009,7 +15012,7 @@
     </row>
     <row r="35" spans="1:10" hidden="1">
       <c r="H35" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I35" s="18">
         <v>46064</v>
@@ -15018,7 +15021,7 @@
     </row>
     <row r="36" spans="1:10" hidden="1">
       <c r="H36" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I36" s="18">
         <v>46070</v>
@@ -15027,7 +15030,7 @@
     </row>
     <row r="37" spans="1:10" hidden="1">
       <c r="H37" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I37" s="18">
         <v>46078</v>
@@ -15036,7 +15039,7 @@
     </row>
     <row r="38" spans="1:10" hidden="1">
       <c r="H38" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I38" s="18">
         <v>46084</v>
@@ -15045,7 +15048,7 @@
     </row>
     <row r="39" spans="1:10" hidden="1">
       <c r="H39" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I39" s="18">
         <v>46092</v>
@@ -15055,7 +15058,7 @@
     <row r="40" spans="1:10" hidden="1">
       <c r="A40" s="5"/>
       <c r="H40" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I40" s="18">
         <v>46099</v>
@@ -15067,7 +15070,7 @@
         <v>16</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I41" s="18">
         <v>46112</v>
@@ -15079,7 +15082,7 @@
         <v>46253</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I42" s="18">
         <v>46120</v>
@@ -15091,13 +15094,13 @@
         <v>46260</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I43" s="18">
         <v>46126</v>
       </c>
       <c r="J43" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="1:10" hidden="1">
@@ -15105,13 +15108,13 @@
         <v>46266</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I44" s="18">
         <v>46134</v>
       </c>
       <c r="J44" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:10" hidden="1">
@@ -15119,13 +15122,13 @@
         <v>46274</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I45" s="18">
         <v>46140</v>
       </c>
       <c r="J45" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="1:10" hidden="1">
@@ -15133,7 +15136,7 @@
         <v>46280</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I46" s="18">
         <v>45951</v>
@@ -15145,7 +15148,7 @@
         <v>46288</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I47" s="18">
         <v>45983</v>
@@ -15157,7 +15160,7 @@
         <v>46294</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I48" s="18">
         <v>45993</v>
@@ -15169,7 +15172,7 @@
         <v>17</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I49" s="18">
         <v>46036</v>
@@ -15178,10 +15181,10 @@
     </row>
     <row r="50" spans="1:10" hidden="1">
       <c r="A50" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I50" s="18">
         <v>46077</v>
@@ -15191,7 +15194,7 @@
     <row r="51" spans="1:10" hidden="1">
       <c r="A51" s="5"/>
       <c r="H51" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I51" s="18">
         <v>46106</v>
@@ -15201,7 +15204,7 @@
     <row r="52" spans="1:10" hidden="1">
       <c r="A52" s="5"/>
       <c r="H52" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I52" s="18">
         <v>46141</v>
@@ -15211,7 +15214,7 @@
     <row r="53" spans="1:10" hidden="1">
       <c r="A53" s="5"/>
       <c r="H53" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I53" s="18">
         <v>46161</v>
@@ -15221,7 +15224,7 @@
     <row r="54" spans="1:10" hidden="1">
       <c r="A54" s="5"/>
       <c r="H54" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I54" s="18">
         <v>46190</v>
@@ -15231,7 +15234,7 @@
     <row r="55" spans="1:10" hidden="1">
       <c r="A55" s="5"/>
       <c r="H55" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I55" s="18">
         <v>46224</v>
@@ -15241,7 +15244,7 @@
     <row r="56" spans="1:10" hidden="1">
       <c r="A56" s="5"/>
       <c r="H56" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I56" s="18">
         <v>46245</v>
@@ -15250,7 +15253,7 @@
     </row>
     <row r="57" spans="1:10" hidden="1">
       <c r="H57" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I57" s="18">
         <v>46295</v>
@@ -15259,7 +15262,7 @@
     </row>
     <row r="58" spans="1:10" hidden="1">
       <c r="H58" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I58" s="18">
         <v>46147</v>
@@ -15268,7 +15271,7 @@
     </row>
     <row r="59" spans="1:10" hidden="1">
       <c r="H59" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I59" s="18">
         <v>46162</v>
@@ -15277,7 +15280,7 @@
     </row>
     <row r="60" spans="1:10" hidden="1">
       <c r="H60" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I60" s="18">
         <v>46168</v>
@@ -15286,7 +15289,7 @@
     </row>
     <row r="61" spans="1:10" hidden="1">
       <c r="H61" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I61" s="18">
         <v>46175</v>
@@ -15295,7 +15298,7 @@
     </row>
     <row r="62" spans="1:10" hidden="1">
       <c r="H62" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I62" s="18">
         <v>46183</v>
@@ -15304,7 +15307,7 @@
     </row>
     <row r="63" spans="1:10" hidden="1">
       <c r="H63" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I63" s="18">
         <v>46189</v>
@@ -15313,7 +15316,7 @@
     </row>
     <row r="64" spans="1:10" hidden="1">
       <c r="H64" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I64" s="18">
         <v>46203</v>
@@ -15322,7 +15325,7 @@
     </row>
     <row r="65" spans="8:14" hidden="1">
       <c r="H65" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I65" s="18">
         <v>46211</v>
@@ -15331,7 +15334,7 @@
     </row>
     <row r="66" spans="8:14" hidden="1">
       <c r="H66" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I66" s="18">
         <v>46217</v>
@@ -15340,7 +15343,7 @@
     </row>
     <row r="67" spans="8:14" hidden="1">
       <c r="H67" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I67" s="18">
         <v>46225</v>
@@ -15349,40 +15352,40 @@
     </row>
     <row r="68" spans="8:14" hidden="1">
       <c r="H68" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I68" s="18">
         <v>46231</v>
       </c>
       <c r="J68" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="69" spans="8:14" hidden="1">
       <c r="H69" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I69" s="18">
         <v>46238</v>
       </c>
       <c r="J69" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="8:14" hidden="1">
       <c r="H70" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I70" s="18">
         <v>46246</v>
       </c>
       <c r="J70" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="8:14" hidden="1">
       <c r="H71" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I71" s="18">
         <v>46253</v>
@@ -15391,7 +15394,7 @@
     </row>
     <row r="72" spans="8:14" hidden="1">
       <c r="H72" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I72" s="18">
         <v>46260</v>
@@ -15400,7 +15403,7 @@
     </row>
     <row r="73" spans="8:14" hidden="1">
       <c r="H73" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I73" s="18">
         <v>46266</v>
@@ -15409,7 +15412,7 @@
     </row>
     <row r="74" spans="8:14" hidden="1">
       <c r="H74" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I74" s="18">
         <v>46274</v>
@@ -15418,7 +15421,7 @@
     </row>
     <row r="75" spans="8:14" hidden="1">
       <c r="H75" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I75" s="18">
         <v>46280</v>
@@ -15427,7 +15430,7 @@
     </row>
     <row r="76" spans="8:14" hidden="1">
       <c r="H76" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I76" s="18">
         <v>46288</v>
@@ -15436,7 +15439,7 @@
     </row>
     <row r="77" spans="8:14" hidden="1">
       <c r="H77" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I77" s="18">
         <v>46294</v>
@@ -15445,7 +15448,7 @@
     </row>
     <row r="78" spans="8:14" hidden="1">
       <c r="H78" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I78" s="18">
         <v>45946</v>
@@ -15462,7 +15465,7 @@
     </row>
     <row r="79" spans="8:14" hidden="1">
       <c r="H79" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I79" s="18">
         <v>45950</v>
@@ -15479,7 +15482,7 @@
     </row>
     <row r="80" spans="8:14" hidden="1">
       <c r="H80" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I80" s="18">
         <v>45982</v>
@@ -15496,7 +15499,7 @@
     </row>
     <row r="81" spans="8:14" hidden="1">
       <c r="H81" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I81" s="18"/>
       <c r="J81" s="16"/>
@@ -15510,7 +15513,7 @@
         <v>11</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J82" s="16"/>
       <c r="K82" s="16"/>
@@ -15523,7 +15526,7 @@
         <v>11</v>
       </c>
       <c r="I83" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J83" s="16"/>
       <c r="K83" s="16"/>
@@ -15536,7 +15539,7 @@
         <v>12</v>
       </c>
       <c r="I84" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J84" s="16"/>
       <c r="K84" s="16"/>
@@ -15549,7 +15552,7 @@
         <v>12</v>
       </c>
       <c r="I85" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J85" s="16"/>
       <c r="K85" s="16"/>
@@ -15559,7 +15562,7 @@
     </row>
     <row r="86" spans="8:14" hidden="1">
       <c r="H86" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I86" s="18">
         <v>45677</v>
@@ -15572,7 +15575,7 @@
     </row>
     <row r="87" spans="8:14" hidden="1">
       <c r="H87" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I87" s="18">
         <v>45739</v>
@@ -15663,7 +15666,7 @@
     </row>
     <row r="94" spans="8:14" hidden="1">
       <c r="H94" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I94" s="18">
         <v>45981</v>
@@ -15678,7 +15681,7 @@
         <v>104</v>
       </c>
       <c r="M94" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N94" s="16" t="s">
         <v>41</v>
@@ -15686,7 +15689,7 @@
     </row>
     <row r="95" spans="8:14" hidden="1">
       <c r="H95" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I95" s="18">
         <v>45672</v>
@@ -15701,7 +15704,7 @@
         <v>104</v>
       </c>
       <c r="M95" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N95" s="16" t="s">
         <v>41</v>
@@ -15709,13 +15712,13 @@
     </row>
     <row r="96" spans="8:14" hidden="1">
       <c r="H96" s="16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I96" s="18">
         <v>45735</v>
       </c>
       <c r="J96" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K96" s="16" t="s">
         <v>76</v>
@@ -15724,7 +15727,7 @@
         <v>104</v>
       </c>
       <c r="M96" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N96" s="16" t="s">
         <v>41</v>
@@ -15732,7 +15735,7 @@
     </row>
     <row r="97" spans="8:10" hidden="1">
       <c r="H97" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I97" s="18">
         <v>45798</v>
@@ -15741,7 +15744,7 @@
     </row>
     <row r="98" spans="8:10" hidden="1">
       <c r="H98" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I98" s="18">
         <v>45854</v>
@@ -15750,7 +15753,7 @@
     </row>
     <row r="99" spans="8:10" hidden="1">
       <c r="H99" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I99" s="18">
         <v>45917</v>
@@ -15804,22 +15807,22 @@
         <v>128</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F2" t="s">
         <v>262</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>262</v>
-      </c>
-      <c r="F2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -15827,22 +15830,22 @@
         <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -15850,22 +15853,22 @@
         <v>131</v>
       </c>
       <c r="B4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D4" t="s">
         <v>262</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>262</v>
       </c>
-      <c r="D4" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" t="s">
-        <v>261</v>
-      </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -15873,22 +15876,22 @@
         <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5" t="s">
         <v>263</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>263</v>
-      </c>
-      <c r="F5" t="s">
-        <v>262</v>
-      </c>
-      <c r="G5" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -15896,22 +15899,22 @@
         <v>133</v>
       </c>
       <c r="B6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" t="s">
         <v>262</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>262</v>
       </c>
-      <c r="D6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E6" t="s">
-        <v>261</v>
-      </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -15919,45 +15922,45 @@
         <v>134</v>
       </c>
       <c r="B7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" t="s">
         <v>263</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>263</v>
       </c>
-      <c r="D7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E7" t="s">
-        <v>262</v>
-      </c>
       <c r="F7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -15965,22 +15968,22 @@
         <v>135</v>
       </c>
       <c r="B9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" t="s">
         <v>263</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>263</v>
       </c>
-      <c r="D9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E9" t="s">
-        <v>262</v>
-      </c>
       <c r="F9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -15988,22 +15991,22 @@
         <v>137</v>
       </c>
       <c r="B10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" t="s">
         <v>263</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>263</v>
       </c>
-      <c r="D10" t="s">
-        <v>262</v>
-      </c>
-      <c r="E10" t="s">
-        <v>262</v>
-      </c>
       <c r="F10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -16011,22 +16014,22 @@
         <v>138</v>
       </c>
       <c r="B11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E11" t="s">
+        <v>264</v>
+      </c>
+      <c r="F11" t="s">
         <v>263</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>263</v>
-      </c>
-      <c r="F11" t="s">
-        <v>262</v>
-      </c>
-      <c r="G11" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -16034,22 +16037,22 @@
         <v>139</v>
       </c>
       <c r="B12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E12" t="s">
+        <v>263</v>
+      </c>
+      <c r="F12" t="s">
         <v>262</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>262</v>
-      </c>
-      <c r="F12" t="s">
-        <v>261</v>
-      </c>
-      <c r="G12" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -16057,22 +16060,22 @@
         <v>140</v>
       </c>
       <c r="B13" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" t="s">
+        <v>263</v>
+      </c>
+      <c r="D13" t="s">
         <v>262</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>262</v>
       </c>
-      <c r="D13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E13" t="s">
-        <v>261</v>
-      </c>
       <c r="F13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -16080,22 +16083,22 @@
         <v>141</v>
       </c>
       <c r="B14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" t="s">
         <v>262</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>262</v>
       </c>
-      <c r="D14" t="s">
-        <v>261</v>
-      </c>
-      <c r="E14" t="s">
-        <v>261</v>
-      </c>
       <c r="F14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -16103,22 +16106,22 @@
         <v>142</v>
       </c>
       <c r="B15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" t="s">
+        <v>264</v>
+      </c>
+      <c r="E15" t="s">
         <v>262</v>
       </c>
-      <c r="C15" t="s">
-        <v>262</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>263</v>
       </c>
-      <c r="E15" t="s">
-        <v>261</v>
-      </c>
-      <c r="F15" t="s">
-        <v>262</v>
-      </c>
       <c r="G15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -16126,22 +16129,22 @@
         <v>143</v>
       </c>
       <c r="B16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D16" t="s">
+        <v>264</v>
+      </c>
+      <c r="E16" t="s">
+        <v>264</v>
+      </c>
+      <c r="F16" t="s">
         <v>263</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>263</v>
-      </c>
-      <c r="F16" t="s">
-        <v>262</v>
-      </c>
-      <c r="G16" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -16149,22 +16152,22 @@
         <v>144</v>
       </c>
       <c r="B17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -16172,45 +16175,45 @@
         <v>145</v>
       </c>
       <c r="B18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D18" t="s">
+        <v>263</v>
+      </c>
+      <c r="E18" t="s">
+        <v>263</v>
+      </c>
+      <c r="F18" t="s">
         <v>262</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>262</v>
-      </c>
-      <c r="F18" t="s">
-        <v>261</v>
-      </c>
-      <c r="G18" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
+        <v>263</v>
+      </c>
+      <c r="E19" t="s">
+        <v>263</v>
+      </c>
+      <c r="F19" t="s">
         <v>262</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>262</v>
-      </c>
-      <c r="F19" t="s">
-        <v>261</v>
-      </c>
-      <c r="G19" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -16220,7 +16223,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09EEA88E-7AEE-574F-BC90-87FF2ABA87C3}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26" style="1" bestFit="1" customWidth="1"/>
@@ -16231,10 +16234,11 @@
     <col min="6" max="6" width="7.125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.875" style="1"/>
+    <col min="9" max="9" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>179</v>
       </c>
@@ -16259,8 +16263,11 @@
       <c r="H1" s="1" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>181</v>
       </c>
@@ -16285,8 +16292,11 @@
       <c r="H2" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>182</v>
       </c>
@@ -16303,7 +16313,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>183</v>
       </c>
@@ -16320,7 +16330,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>184</v>
       </c>
@@ -16337,7 +16347,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>185</v>
       </c>
@@ -16349,7 +16359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>186</v>
       </c>
@@ -16361,7 +16371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>187</v>
       </c>
@@ -16373,7 +16383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>188</v>
       </c>
@@ -16385,7 +16395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>189</v>
       </c>
@@ -16397,7 +16407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>190</v>
       </c>
@@ -16409,7 +16419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>192</v>
       </c>
@@ -16421,7 +16431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>193</v>
       </c>
@@ -16433,7 +16443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>194</v>
       </c>
@@ -16445,7 +16455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="C15" s="22" t="s">
         <v>195</v>
       </c>
@@ -16456,7 +16466,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>198</v>
       </c>
@@ -18536,6 +18546,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -18718,25 +18745,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18744,5 +18754,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}"/>
 </file>
--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B49C4EA-3204-479D-91E5-4149CC0A998E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B18D7B0-468F-4896-8E47-ADC4B6407FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31470" yWindow="720" windowWidth="22995" windowHeight="13260" activeTab="2" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
+    <workbookView xWindow="31470" yWindow="720" windowWidth="22995" windowHeight="13260" firstSheet="2" activeTab="2" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
   <sheets>
     <sheet name="Class_Enrollment" sheetId="1" r:id="rId1"/>
@@ -18546,23 +18546,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -18745,8 +18728,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18754,5 +18754,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}"/>
 </file>
--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B18D7B0-468F-4896-8E47-ADC4B6407FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC58811A-269C-4762-8E64-209812415BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31470" yWindow="720" windowWidth="22995" windowHeight="13260" firstSheet="2" activeTab="2" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
+    <workbookView xWindow="31470" yWindow="720" windowWidth="22995" windowHeight="13260" firstSheet="2" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
   <sheets>
     <sheet name="Class_Enrollment" sheetId="1" r:id="rId1"/>
@@ -358,7 +358,7 @@
     <t>Payton</t>
   </si>
   <si>
-    <t>Phalen</t>
+    <t>Phelan</t>
   </si>
   <si>
     <t>Pepin</t>

--- a/training/upload/MASTER Education Classes Roster.xlsx
+++ b/training/upload/MASTER Education Classes Roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/training/upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E848DCF-F5A5-C64F-9009-9E17E1B23370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E270286-6CDA-5F42-951D-DDEE1EC5787C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="17260" xr2:uid="{5604E27C-0991-9B4E-A9D1-5F87A876A78F}"/>
   </bookViews>
   <sheets>
     <sheet name="Class_Enrollment" sheetId="1" r:id="rId1"/>
@@ -1287,17 +1287,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5C9BF4B3-A48F-BE48-B38E-211555B96796}" name="Table2" displayName="Table2" ref="A1:Z144" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
-  <autoFilter ref="A1:Z144" xr:uid="{5C9BF4B3-A48F-BE48-B38E-211555B96796}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="AMT"/>
-        <filter val="ATP"/>
-        <filter val="CCEMT"/>
-        <filter val="MEDIC"/>
-        <filter val="NURSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Z144" xr:uid="{5C9BF4B3-A48F-BE48-B38E-211555B96796}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z144">
     <sortCondition descending="1" ref="B1:B144"/>
   </sortState>
@@ -3792,7 +3782,7 @@
     </row>
     <row r="28" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>263</v>
+        <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>27</v>
@@ -3810,16 +3800,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="b">
         <v>0</v>
@@ -3828,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2" t="b">
         <v>0</v>
@@ -3837,28 +3827,28 @@
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="2" t="b">
         <v>1</v>
@@ -3869,7 +3859,7 @@
     </row>
     <row r="29" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>27</v>
@@ -3887,16 +3877,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
@@ -3905,10 +3895,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="2" t="b">
         <v>0</v>
@@ -3917,25 +3907,25 @@
         <v>0</v>
       </c>
       <c r="R29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="2" t="b">
         <v>1</v>
@@ -3946,7 +3936,7 @@
     </row>
     <row r="30" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>27</v>
@@ -3994,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="R30" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" s="2" t="b">
         <v>1</v>
@@ -4023,13 +4013,13 @@
     </row>
     <row r="31" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="2" t="b">
         <v>0</v>
@@ -4065,10 +4055,10 @@
         <v>1</v>
       </c>
       <c r="P31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="2" t="b">
         <v>0</v>
@@ -4100,7 +4090,7 @@
     </row>
     <row r="32" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>27</v>
@@ -4145,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="Q32" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" s="2" t="b">
         <v>0</v>
@@ -4177,13 +4167,13 @@
     </row>
     <row r="33" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="2" t="b">
         <v>0</v>
@@ -4213,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2" t="b">
         <v>1</v>
@@ -4254,7 +4244,7 @@
     </row>
     <row r="34" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>27</v>
@@ -4290,16 +4280,16 @@
         <v>0</v>
       </c>
       <c r="N34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="2" t="b">
         <v>0</v>
@@ -7133,7 +7123,7 @@
     </row>
     <row r="71" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>68</v>
@@ -7151,25 +7141,25 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" s="2" t="b">
         <v>0</v>
@@ -7178,28 +7168,28 @@
         <v>0</v>
       </c>
       <c r="Q71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71" s="2" t="b">
         <v>1</v>
@@ -7210,7 +7200,7 @@
     </row>
     <row r="72" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>68</v>
@@ -7228,25 +7218,25 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" s="2" t="b">
         <v>0</v>
@@ -7255,28 +7245,28 @@
         <v>0</v>
       </c>
       <c r="Q72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X72" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y72" s="2" t="b">
         <v>1</v>
@@ -8055,7 +8045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>108</v>
       </c>
@@ -8084,7 +8074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>110</v>
       </c>
@@ -8113,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>111</v>
       </c>
@@ -8142,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>112</v>
       </c>
@@ -8171,7 +8161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>113</v>
       </c>
@@ -8200,7 +8190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>114</v>
       </c>
@@ -8229,7 +8219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>115</v>
       </c>
@@ -8258,7 +8248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>116</v>
       </c>
@@ -8287,7 +8277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>117</v>
       </c>
@@ -8316,7 +8306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>118</v>
       </c>
@@ -8345,7 +8335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>119</v>
       </c>
@@ -8374,7 +8364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>120</v>
       </c>
@@ -8403,7 +8393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>121</v>
       </c>
@@ -8432,7 +8422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>122</v>
       </c>
@@ -8461,7 +8451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>123</v>
       </c>
@@ -8490,7 +8480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:26" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>124</v>
       </c>
@@ -18316,6 +18306,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -18498,24 +18505,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14BDA993-1F92-4F2B-A479-4671916F14AA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18532,22 +18540,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3643D-FDE0-44DC-9CDA-200C2597DFB6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13094262-B8A9-472E-A55D-BC65572C19CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>